--- a/research/traditional_assets/database/data/bangladesh/bangladesh_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_computers_peripherals.xlsx
@@ -1270,7 +1270,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1407,22 +1407,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1913679588811317</v>
+        <v>0.1908253550044883</v>
       </c>
       <c r="C2">
-        <v>28.38290978133732</v>
+        <v>28.20148102912485</v>
       </c>
       <c r="D2">
-        <v>28.00290978133732</v>
+        <v>28.10768102912485</v>
       </c>
       <c r="E2">
-        <v>-2.32</v>
+        <v>-2.0338</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2862</v>
       </c>
       <c r="G2">
         <v>0.38</v>
@@ -1443,28 +1443,28 @@
         <v>0.573</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01439586</v>
       </c>
       <c r="N2">
-        <v>0.573</v>
+        <v>0.5586041399999999</v>
       </c>
       <c r="O2">
-        <v>0.1719</v>
+        <v>0.167581242</v>
       </c>
       <c r="P2">
-        <v>0.4011</v>
+        <v>0.391022898</v>
       </c>
       <c r="Q2">
-        <v>-0.1718999999999999</v>
+        <v>-0.181977102</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1913679588811317</v>
+        <v>0.1923972272772609</v>
       </c>
       <c r="T2">
-        <v>1.246903653332528</v>
+        <v>1.255720143810636</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>39.80311006080915</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1489,22 +1489,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1908253550044883</v>
+        <v>0.1902827511278449</v>
       </c>
       <c r="C3">
-        <v>28.20148102912485</v>
+        <v>28.02083921216612</v>
       </c>
       <c r="D3">
-        <v>28.10768102912485</v>
+        <v>28.21323921216612</v>
       </c>
       <c r="E3">
-        <v>-2.0338</v>
+        <v>-1.7476</v>
       </c>
       <c r="F3">
-        <v>0.2862</v>
+        <v>0.5724</v>
       </c>
       <c r="G3">
         <v>0.38</v>
@@ -1525,28 +1525,28 @@
         <v>0.573</v>
       </c>
       <c r="M3">
-        <v>0.01439586</v>
+        <v>0.02879172</v>
       </c>
       <c r="N3">
-        <v>0.5586041399999999</v>
+        <v>0.54420828</v>
       </c>
       <c r="O3">
-        <v>0.167581242</v>
+        <v>0.163262484</v>
       </c>
       <c r="P3">
-        <v>0.391022898</v>
+        <v>0.380945796</v>
       </c>
       <c r="Q3">
-        <v>-0.181977102</v>
+        <v>-0.192054204</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1923972272772609</v>
+        <v>0.1934475011508622</v>
       </c>
       <c r="T3">
-        <v>1.255720143810636</v>
+        <v>1.264716562665849</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>39.80311006080915</v>
+        <v>19.90155503040457</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1571,22 +1571,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1902827511278449</v>
+        <v>0.1897401472512015</v>
       </c>
       <c r="C4">
-        <v>28.02083921216612</v>
+        <v>27.84099322987094</v>
       </c>
       <c r="D4">
-        <v>28.21323921216612</v>
+        <v>28.31959322987094</v>
       </c>
       <c r="E4">
-        <v>-1.7476</v>
+        <v>-1.4614</v>
       </c>
       <c r="F4">
-        <v>0.5724</v>
+        <v>0.8586</v>
       </c>
       <c r="G4">
         <v>0.38</v>
@@ -1607,28 +1607,28 @@
         <v>0.573</v>
       </c>
       <c r="M4">
-        <v>0.02879172</v>
+        <v>0.04318758</v>
       </c>
       <c r="N4">
-        <v>0.54420828</v>
+        <v>0.52981242</v>
       </c>
       <c r="O4">
-        <v>0.163262484</v>
+        <v>0.158943726</v>
       </c>
       <c r="P4">
-        <v>0.380945796</v>
+        <v>0.370868694</v>
       </c>
       <c r="Q4">
-        <v>-0.192054204</v>
+        <v>-0.202131306</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1934475011508622</v>
+        <v>0.1945194301558778</v>
       </c>
       <c r="T4">
-        <v>1.264716562665849</v>
+        <v>1.273898474693335</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>19.90155503040457</v>
+        <v>13.26770335360305</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1653,22 +1653,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1897401472512015</v>
+        <v>0.1892871433745581</v>
       </c>
       <c r="C5">
-        <v>27.84099322987094</v>
+        <v>27.64420113929322</v>
       </c>
       <c r="D5">
-        <v>28.31959322987094</v>
+        <v>28.40900113929322</v>
       </c>
       <c r="E5">
-        <v>-1.4614</v>
+        <v>-1.1752</v>
       </c>
       <c r="F5">
-        <v>0.8586</v>
+        <v>1.1448</v>
       </c>
       <c r="G5">
         <v>0.38</v>
@@ -1689,45 +1689,45 @@
         <v>0.573</v>
       </c>
       <c r="M5">
-        <v>0.04318758</v>
+        <v>0.0612468</v>
       </c>
       <c r="N5">
-        <v>0.52981242</v>
+        <v>0.5117531999999999</v>
       </c>
       <c r="O5">
-        <v>0.158943726</v>
+        <v>0.15352596</v>
       </c>
       <c r="P5">
-        <v>0.370868694</v>
+        <v>0.3582272399999999</v>
       </c>
       <c r="Q5">
-        <v>-0.202131306</v>
+        <v>-0.21477276</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1945194301558778</v>
+        <v>0.1956136910151647</v>
       </c>
       <c r="T5">
-        <v>1.273898474693335</v>
+        <v>1.283271676554726</v>
       </c>
       <c r="U5">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.3</v>
       </c>
       <c r="W5">
-        <v>0.03521</v>
+        <v>0.03745</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>13.26770335360305</v>
+        <v>9.355590822704205</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1735,22 +1735,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1892871433745581</v>
+        <v>0.1887949394979147</v>
       </c>
       <c r="C6">
-        <v>27.64420113929322</v>
+        <v>27.4557879598718</v>
       </c>
       <c r="D6">
-        <v>28.40900113929322</v>
+        <v>28.5067879598718</v>
       </c>
       <c r="E6">
-        <v>-1.1752</v>
+        <v>-0.8889999999999998</v>
       </c>
       <c r="F6">
-        <v>1.1448</v>
+        <v>1.431</v>
       </c>
       <c r="G6">
         <v>0.38</v>
@@ -1771,45 +1771,45 @@
         <v>0.573</v>
       </c>
       <c r="M6">
-        <v>0.0612468</v>
+        <v>0.0777033</v>
       </c>
       <c r="N6">
-        <v>0.5117531999999999</v>
+        <v>0.4952966999999999</v>
       </c>
       <c r="O6">
-        <v>0.15352596</v>
+        <v>0.14858901</v>
       </c>
       <c r="P6">
-        <v>0.3582272399999999</v>
+        <v>0.34670769</v>
       </c>
       <c r="Q6">
-        <v>-0.21477276</v>
+        <v>-0.22629231</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1956136910151647</v>
+        <v>0.1967309889451734</v>
       </c>
       <c r="T6">
-        <v>1.283271676554726</v>
+        <v>1.292842208981621</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V6">
         <v>0.3</v>
       </c>
       <c r="W6">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y6">
-        <v>9.355590822704205</v>
+        <v>7.374204184378269</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1817,22 +1817,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1887949394979147</v>
+        <v>0.1882803356212713</v>
       </c>
       <c r="C7">
-        <v>27.4557879598718</v>
+        <v>27.27254745621798</v>
       </c>
       <c r="D7">
-        <v>28.5067879598718</v>
+        <v>28.60974745621798</v>
       </c>
       <c r="E7">
-        <v>-0.8889999999999998</v>
+        <v>-0.6027999999999996</v>
       </c>
       <c r="F7">
-        <v>1.431</v>
+        <v>1.7172</v>
       </c>
       <c r="G7">
         <v>0.38</v>
@@ -1853,28 +1853,28 @@
         <v>0.573</v>
       </c>
       <c r="M7">
-        <v>0.0777033</v>
+        <v>0.09324396000000001</v>
       </c>
       <c r="N7">
-        <v>0.4952966999999999</v>
+        <v>0.4797560399999999</v>
       </c>
       <c r="O7">
-        <v>0.14858901</v>
+        <v>0.143926812</v>
       </c>
       <c r="P7">
-        <v>0.34670769</v>
+        <v>0.3358292279999999</v>
       </c>
       <c r="Q7">
-        <v>-0.22629231</v>
+        <v>-0.237170772</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1967309889451734</v>
+        <v>0.1978720591715653</v>
       </c>
       <c r="T7">
-        <v>1.292842208981621</v>
+        <v>1.302616369758024</v>
       </c>
       <c r="U7">
         <v>0.0543</v>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>7.374204184378269</v>
+        <v>6.145170153648556</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1882803356212713</v>
+        <v>0.187814731744628</v>
       </c>
       <c r="C8">
-        <v>27.27254745621799</v>
+        <v>27.08014624146905</v>
       </c>
       <c r="D8">
-        <v>28.60974745621798</v>
+        <v>28.70354624146905</v>
       </c>
       <c r="E8">
-        <v>-0.6027999999999998</v>
+        <v>-0.3165999999999998</v>
       </c>
       <c r="F8">
-        <v>1.7172</v>
+        <v>2.0034</v>
       </c>
       <c r="G8">
         <v>0.38</v>
@@ -1935,45 +1935,45 @@
         <v>0.573</v>
       </c>
       <c r="M8">
-        <v>0.09324396</v>
+        <v>0.11078802</v>
       </c>
       <c r="N8">
-        <v>0.4797560399999999</v>
+        <v>0.46221198</v>
       </c>
       <c r="O8">
-        <v>0.143926812</v>
+        <v>0.138663594</v>
       </c>
       <c r="P8">
-        <v>0.3358292279999999</v>
+        <v>0.323548386</v>
       </c>
       <c r="Q8">
-        <v>-0.237170772</v>
+        <v>-0.2494516139999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1978720591715653</v>
+        <v>0.1990376685426107</v>
       </c>
       <c r="T8">
-        <v>1.302616369758024</v>
+        <v>1.312600727540371</v>
       </c>
       <c r="U8">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V8">
         <v>0.3</v>
       </c>
       <c r="W8">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y8">
-        <v>6.145170153648557</v>
+        <v>5.172039359490313</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1981,22 +1981,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.187814731744628</v>
+        <v>0.1873071278679846</v>
       </c>
       <c r="C9">
-        <v>27.08014624146905</v>
+        <v>26.89690947424116</v>
       </c>
       <c r="D9">
-        <v>28.70354624146905</v>
+        <v>28.80650947424116</v>
       </c>
       <c r="E9">
-        <v>-0.3165999999999998</v>
+        <v>-0.03039999999999976</v>
       </c>
       <c r="F9">
-        <v>2.0034</v>
+        <v>2.2896</v>
       </c>
       <c r="G9">
         <v>0.38</v>
@@ -2017,28 +2017,28 @@
         <v>0.573</v>
       </c>
       <c r="M9">
-        <v>0.11078802</v>
+        <v>0.12661488</v>
       </c>
       <c r="N9">
-        <v>0.46221198</v>
+        <v>0.44638512</v>
       </c>
       <c r="O9">
-        <v>0.138663594</v>
+        <v>0.133915536</v>
       </c>
       <c r="P9">
-        <v>0.323548386</v>
+        <v>0.312469584</v>
       </c>
       <c r="Q9">
-        <v>-0.2494516139999999</v>
+        <v>-0.2605304159999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1990376685426107</v>
+        <v>0.2002286172478093</v>
       </c>
       <c r="T9">
-        <v>1.312600727540371</v>
+        <v>1.322802136578856</v>
       </c>
       <c r="U9">
         <v>0.0553</v>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>5.172039359490313</v>
+        <v>4.525534439554024</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2063,22 +2063,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1873071278679846</v>
+        <v>0.1871775239913412</v>
       </c>
       <c r="C10">
-        <v>26.89690947424116</v>
+        <v>26.6371170332012</v>
       </c>
       <c r="D10">
-        <v>28.80650947424116</v>
+        <v>28.8329170332012</v>
       </c>
       <c r="E10">
-        <v>-0.03039999999999976</v>
+        <v>0.2558000000000002</v>
       </c>
       <c r="F10">
-        <v>2.2896</v>
+        <v>2.5758</v>
       </c>
       <c r="G10">
         <v>0.38</v>
@@ -2099,45 +2099,45 @@
         <v>0.573</v>
       </c>
       <c r="M10">
-        <v>0.12661488</v>
+        <v>0.15789654</v>
       </c>
       <c r="N10">
-        <v>0.44638512</v>
+        <v>0.41510346</v>
       </c>
       <c r="O10">
-        <v>0.133915536</v>
+        <v>0.124531038</v>
       </c>
       <c r="P10">
-        <v>0.312469584</v>
+        <v>0.290572422</v>
       </c>
       <c r="Q10">
-        <v>-0.2605304159999999</v>
+        <v>-0.282427578</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2002286172478093</v>
+        <v>0.2014457406498254</v>
       </c>
       <c r="T10">
-        <v>1.322802136578856</v>
+        <v>1.333227752409395</v>
       </c>
       <c r="U10">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V10">
         <v>0.3</v>
       </c>
       <c r="W10">
-        <v>0.03871</v>
+        <v>0.04291</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>4.525534439554024</v>
+        <v>3.628958557293275</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2145,22 +2145,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1871775239913412</v>
+        <v>0.1869079201146978</v>
       </c>
       <c r="C11">
-        <v>26.6371170332012</v>
+        <v>26.40600583474239</v>
       </c>
       <c r="D11">
-        <v>28.8329170332012</v>
+        <v>28.88800583474239</v>
       </c>
       <c r="E11">
-        <v>0.2558000000000002</v>
+        <v>0.5419999999999998</v>
       </c>
       <c r="F11">
-        <v>2.5758</v>
+        <v>2.862</v>
       </c>
       <c r="G11">
         <v>0.38</v>
@@ -2181,45 +2181,45 @@
         <v>0.573</v>
       </c>
       <c r="M11">
-        <v>0.15789654</v>
+        <v>0.1834542</v>
       </c>
       <c r="N11">
-        <v>0.41510346</v>
+        <v>0.3895457999999999</v>
       </c>
       <c r="O11">
-        <v>0.124531038</v>
+        <v>0.11686374</v>
       </c>
       <c r="P11">
-        <v>0.290572422</v>
+        <v>0.2726820599999999</v>
       </c>
       <c r="Q11">
-        <v>-0.282427578</v>
+        <v>-0.30031794</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2014457406498254</v>
+        <v>0.2026899112385531</v>
       </c>
       <c r="T11">
-        <v>1.333227752409395</v>
+        <v>1.343885048591724</v>
       </c>
       <c r="U11">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V11">
         <v>0.3</v>
       </c>
       <c r="W11">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y11">
-        <v>3.628958557293275</v>
+        <v>3.123395376066615</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2227,22 +2227,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1869079201146978</v>
+        <v>0.1870625162380544</v>
       </c>
       <c r="C12">
-        <v>26.40600583474239</v>
+        <v>26.08819112312258</v>
       </c>
       <c r="D12">
-        <v>28.88800583474239</v>
+        <v>28.85639112312258</v>
       </c>
       <c r="E12">
-        <v>0.5420000000000003</v>
+        <v>0.8282000000000003</v>
       </c>
       <c r="F12">
-        <v>2.862</v>
+        <v>3.1482</v>
       </c>
       <c r="G12">
         <v>0.38</v>
@@ -2263,45 +2263,45 @@
         <v>0.573</v>
       </c>
       <c r="M12">
-        <v>0.1834542</v>
+        <v>0.22635558</v>
       </c>
       <c r="N12">
-        <v>0.3895457999999999</v>
+        <v>0.34664442</v>
       </c>
       <c r="O12">
-        <v>0.11686374</v>
+        <v>0.103993326</v>
       </c>
       <c r="P12">
-        <v>0.2726820599999999</v>
+        <v>0.242651094</v>
       </c>
       <c r="Q12">
-        <v>-0.30031794</v>
+        <v>-0.330348906</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2026899112385531</v>
+        <v>0.203962040716915</v>
       </c>
       <c r="T12">
-        <v>1.343885048591724</v>
+        <v>1.354781834575904</v>
       </c>
       <c r="U12">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>3.123395376066615</v>
+        <v>2.531415395193704</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2309,22 +2309,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1870625162380544</v>
+        <v>0.186998712361411</v>
       </c>
       <c r="C13">
-        <v>26.08819112312258</v>
+        <v>25.81503054528729</v>
       </c>
       <c r="D13">
-        <v>28.85639112312258</v>
+        <v>28.86943054528729</v>
       </c>
       <c r="E13">
-        <v>0.8282000000000003</v>
+        <v>1.1144</v>
       </c>
       <c r="F13">
-        <v>3.1482</v>
+        <v>3.4344</v>
       </c>
       <c r="G13">
         <v>0.38</v>
@@ -2345,45 +2345,45 @@
         <v>0.573</v>
       </c>
       <c r="M13">
-        <v>0.22635558</v>
+        <v>0.26032752</v>
       </c>
       <c r="N13">
-        <v>0.34664442</v>
+        <v>0.3126724799999999</v>
       </c>
       <c r="O13">
-        <v>0.103993326</v>
+        <v>0.09380174399999998</v>
       </c>
       <c r="P13">
-        <v>0.242651094</v>
+        <v>0.218870736</v>
       </c>
       <c r="Q13">
-        <v>-0.330348906</v>
+        <v>-0.354129264</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.203962040716915</v>
+        <v>0.2052630822288761</v>
       </c>
       <c r="T13">
-        <v>1.354781834575904</v>
+        <v>1.365926274786996</v>
       </c>
       <c r="U13">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y13">
-        <v>2.531415395193704</v>
+        <v>2.201073478516601</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2391,22 +2391,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.186998712361411</v>
+        <v>0.1866346084847676</v>
       </c>
       <c r="C14">
-        <v>25.81503054528729</v>
+        <v>25.603467537509</v>
       </c>
       <c r="D14">
-        <v>28.86943054528729</v>
+        <v>28.944067537509</v>
       </c>
       <c r="E14">
-        <v>1.1144</v>
+        <v>1.4006</v>
       </c>
       <c r="F14">
-        <v>3.4344</v>
+        <v>3.7206</v>
       </c>
       <c r="G14">
         <v>0.38</v>
@@ -2427,28 +2427,28 @@
         <v>0.573</v>
       </c>
       <c r="M14">
-        <v>0.26032752</v>
+        <v>0.28202148</v>
       </c>
       <c r="N14">
-        <v>0.3126724799999999</v>
+        <v>0.2909785199999999</v>
       </c>
       <c r="O14">
-        <v>0.09380174399999998</v>
+        <v>0.08729355599999997</v>
       </c>
       <c r="P14">
-        <v>0.218870736</v>
+        <v>0.2036849639999999</v>
       </c>
       <c r="Q14">
-        <v>-0.354129264</v>
+        <v>-0.369315036</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2052630822288761</v>
+        <v>0.2065940327411122</v>
       </c>
       <c r="T14">
-        <v>1.365926274786996</v>
+        <v>1.37732690902593</v>
       </c>
       <c r="U14">
         <v>0.07580000000000001</v>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>2.201073478516601</v>
+        <v>2.031760134015324</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2473,22 +2473,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1866346084847676</v>
+        <v>0.1876621046081242</v>
       </c>
       <c r="C15">
-        <v>25.603467537509</v>
+        <v>25.10762792112861</v>
       </c>
       <c r="D15">
-        <v>28.944067537509</v>
+        <v>28.73442792112861</v>
       </c>
       <c r="E15">
-        <v>1.4006</v>
+        <v>1.6868</v>
       </c>
       <c r="F15">
-        <v>3.7206</v>
+        <v>4.0068</v>
       </c>
       <c r="G15">
         <v>0.38</v>
@@ -2509,45 +2509,45 @@
         <v>0.573</v>
       </c>
       <c r="M15">
-        <v>0.28202148</v>
+        <v>0.360612</v>
       </c>
       <c r="N15">
-        <v>0.2909785199999999</v>
+        <v>0.212388</v>
       </c>
       <c r="O15">
-        <v>0.08729355599999997</v>
+        <v>0.06371639999999999</v>
       </c>
       <c r="P15">
-        <v>0.2036849639999999</v>
+        <v>0.1486716</v>
       </c>
       <c r="Q15">
-        <v>-0.369315036</v>
+        <v>-0.4243284</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2065940327411122</v>
+        <v>0.2079559355908421</v>
       </c>
       <c r="T15">
-        <v>1.37732690902593</v>
+        <v>1.388992674293676</v>
       </c>
       <c r="U15">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>2.031760134015324</v>
+        <v>1.588965425443413</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2555,22 +2555,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1876621046081242</v>
+        <v>0.194555788952787</v>
       </c>
       <c r="C16">
-        <v>25.10762792112861</v>
+        <v>23.48980864562199</v>
       </c>
       <c r="D16">
-        <v>28.73442792112861</v>
+        <v>27.402808645622</v>
       </c>
       <c r="E16">
-        <v>1.6868</v>
+        <v>1.973000000000001</v>
       </c>
       <c r="F16">
-        <v>4.0068</v>
+        <v>4.293000000000001</v>
       </c>
       <c r="G16">
         <v>0.38</v>
@@ -2591,45 +2591,45 @@
         <v>0.573</v>
       </c>
       <c r="M16">
-        <v>0.360612</v>
+        <v>0.6302124000000002</v>
       </c>
       <c r="N16">
-        <v>0.212388</v>
+        <v>-0.05721240000000027</v>
       </c>
       <c r="O16">
-        <v>0.06371639999999999</v>
+        <v>-0.01716372000000008</v>
       </c>
       <c r="P16">
-        <v>0.1486716</v>
+        <v>-0.0400486800000002</v>
       </c>
       <c r="Q16">
-        <v>-0.4243284</v>
+        <v>-0.6130486800000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2079559355908421</v>
+        <v>0.2100495038364271</v>
       </c>
       <c r="T16">
-        <v>1.388992674293676</v>
+        <v>1.406925727102726</v>
       </c>
       <c r="U16">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V16">
-        <v>0.3</v>
+        <v>0.272765182024346</v>
       </c>
       <c r="W16">
-        <v>0.063</v>
+        <v>0.106758071278826</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y16">
-        <v>1.588965425443413</v>
+        <v>0.9092172734144865</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2637,22 +2637,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.194555788952787</v>
+        <v>0.195565788952787</v>
       </c>
       <c r="C17">
-        <v>23.489808645622</v>
+        <v>23.01880785149135</v>
       </c>
       <c r="D17">
-        <v>27.402808645622</v>
+        <v>27.21800785149135</v>
       </c>
       <c r="E17">
-        <v>1.973</v>
+        <v>2.2592</v>
       </c>
       <c r="F17">
-        <v>4.293</v>
+        <v>4.5792</v>
       </c>
       <c r="G17">
         <v>0.38</v>
@@ -2673,37 +2673,37 @@
         <v>0.573</v>
       </c>
       <c r="M17">
-        <v>0.6302124000000001</v>
+        <v>0.6722265600000001</v>
       </c>
       <c r="N17">
-        <v>-0.05721240000000016</v>
+        <v>-0.09922656000000019</v>
       </c>
       <c r="O17">
-        <v>-0.01716372000000005</v>
+        <v>-0.02976796800000005</v>
       </c>
       <c r="P17">
-        <v>-0.04004868000000011</v>
+        <v>-0.06945859200000012</v>
       </c>
       <c r="Q17">
-        <v>-0.6130486800000001</v>
+        <v>-0.6424585920000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2100495038364271</v>
+        <v>0.2120048550725751</v>
       </c>
       <c r="T17">
-        <v>1.406925727102726</v>
+        <v>1.423674842901568</v>
       </c>
       <c r="U17">
         <v>0.1468</v>
       </c>
       <c r="V17">
-        <v>0.272765182024346</v>
+        <v>0.2557173581478244</v>
       </c>
       <c r="W17">
-        <v>0.106758071278826</v>
+        <v>0.1092606918238994</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.9092172734144867</v>
+        <v>0.8523911938260813</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2719,22 +2719,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.195565788952787</v>
+        <v>0.1965757889527869</v>
       </c>
       <c r="C18">
-        <v>23.01880785149135</v>
+        <v>22.55028290316285</v>
       </c>
       <c r="D18">
-        <v>27.21800785149135</v>
+        <v>27.03568290316285</v>
       </c>
       <c r="E18">
-        <v>2.2592</v>
+        <v>2.5454</v>
       </c>
       <c r="F18">
-        <v>4.5792</v>
+        <v>4.8654</v>
       </c>
       <c r="G18">
         <v>0.38</v>
@@ -2755,37 +2755,37 @@
         <v>0.573</v>
       </c>
       <c r="M18">
-        <v>0.6722265600000001</v>
+        <v>0.7142407200000001</v>
       </c>
       <c r="N18">
-        <v>-0.09922656000000019</v>
+        <v>-0.1412407200000001</v>
       </c>
       <c r="O18">
-        <v>-0.02976796800000005</v>
+        <v>-0.04237221600000003</v>
       </c>
       <c r="P18">
-        <v>-0.06945859200000012</v>
+        <v>-0.09886850400000008</v>
       </c>
       <c r="Q18">
-        <v>-0.6424585920000001</v>
+        <v>-0.6718685040000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2120048550725751</v>
+        <v>0.2140073232059796</v>
       </c>
       <c r="T18">
-        <v>1.423674842901568</v>
+        <v>1.44082755185219</v>
       </c>
       <c r="U18">
         <v>0.1468</v>
       </c>
       <c r="V18">
-        <v>0.2557173581478244</v>
+        <v>0.2406751606097171</v>
       </c>
       <c r="W18">
-        <v>0.1092606918238994</v>
+        <v>0.1114688864224935</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.8523911938260813</v>
+        <v>0.8022505353657237</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2801,22 +2801,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1965757889527869</v>
+        <v>0.2089074699960594</v>
       </c>
       <c r="C19">
-        <v>22.55028290316285</v>
+        <v>20.22005991416723</v>
       </c>
       <c r="D19">
-        <v>27.03568290316285</v>
+        <v>24.99165991416723</v>
       </c>
       <c r="E19">
-        <v>2.5454</v>
+        <v>2.831600000000001</v>
       </c>
       <c r="F19">
-        <v>4.8654</v>
+        <v>5.151600000000001</v>
       </c>
       <c r="G19">
         <v>0.38</v>
@@ -2837,45 +2837,45 @@
         <v>0.573</v>
       </c>
       <c r="M19">
-        <v>0.7142407200000001</v>
+        <v>1.03444128</v>
       </c>
       <c r="N19">
-        <v>-0.1412407200000001</v>
+        <v>-0.4614412800000003</v>
       </c>
       <c r="O19">
-        <v>-0.04237221600000003</v>
+        <v>-0.1384323840000001</v>
       </c>
       <c r="P19">
-        <v>-0.09886850400000008</v>
+        <v>-0.3230088960000002</v>
       </c>
       <c r="Q19">
-        <v>-0.6718685040000001</v>
+        <v>-0.8960088960000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2140073232059796</v>
+        <v>0.2180119015905311</v>
       </c>
       <c r="T19">
-        <v>1.44082755185219</v>
+        <v>1.475129904211415</v>
       </c>
       <c r="U19">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V19">
-        <v>0.2406751606097171</v>
+        <v>0.1661766630194804</v>
       </c>
       <c r="W19">
-        <v>0.1114688864224935</v>
+        <v>0.1674317260656883</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y19">
-        <v>0.8022505353657237</v>
+        <v>0.5539222100649346</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2883,22 +2883,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2089074699960594</v>
+        <v>0.2104574699960594</v>
       </c>
       <c r="C20">
-        <v>20.22005991416723</v>
+        <v>19.69860139314243</v>
       </c>
       <c r="D20">
-        <v>24.99165991416723</v>
+        <v>24.75640139314243</v>
       </c>
       <c r="E20">
-        <v>2.8316</v>
+        <v>3.1178</v>
       </c>
       <c r="F20">
-        <v>5.1516</v>
+        <v>5.4378</v>
       </c>
       <c r="G20">
         <v>0.38</v>
@@ -2919,37 +2919,37 @@
         <v>0.573</v>
       </c>
       <c r="M20">
-        <v>1.03444128</v>
+        <v>1.09191024</v>
       </c>
       <c r="N20">
-        <v>-0.4614412800000001</v>
+        <v>-0.5189102400000001</v>
       </c>
       <c r="O20">
-        <v>-0.138432384</v>
+        <v>-0.155673072</v>
       </c>
       <c r="P20">
-        <v>-0.323008896</v>
+        <v>-0.3632371680000001</v>
       </c>
       <c r="Q20">
-        <v>-0.896008896</v>
+        <v>-0.936237168</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2180119015905311</v>
+        <v>0.2201379744496735</v>
       </c>
       <c r="T20">
-        <v>1.475129904211415</v>
+        <v>1.493341384510321</v>
       </c>
       <c r="U20">
         <v>0.2008</v>
       </c>
       <c r="V20">
-        <v>0.1661766630194804</v>
+        <v>0.1574305228605604</v>
       </c>
       <c r="W20">
-        <v>0.1674317260656883</v>
+        <v>0.1691879510095995</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.5539222100649347</v>
+        <v>0.5247684095352013</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2104574699960594</v>
+        <v>0.2196537676431814</v>
       </c>
       <c r="C21">
-        <v>19.69860139314243</v>
+        <v>18.10286845077773</v>
       </c>
       <c r="D21">
-        <v>24.75640139314243</v>
+        <v>23.44686845077773</v>
       </c>
       <c r="E21">
-        <v>3.1178</v>
+        <v>3.404</v>
       </c>
       <c r="F21">
-        <v>5.4378</v>
+        <v>5.724</v>
       </c>
       <c r="G21">
         <v>0.38</v>
@@ -3001,45 +3001,45 @@
         <v>0.573</v>
       </c>
       <c r="M21">
-        <v>1.09191024</v>
+        <v>1.3497192</v>
       </c>
       <c r="N21">
-        <v>-0.5189102400000001</v>
+        <v>-0.7767192000000001</v>
       </c>
       <c r="O21">
-        <v>-0.155673072</v>
+        <v>-0.23301576</v>
       </c>
       <c r="P21">
-        <v>-0.3632371680000001</v>
+        <v>-0.54370344</v>
       </c>
       <c r="Q21">
-        <v>-0.936237168</v>
+        <v>-1.11670344</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2201379744496735</v>
+        <v>0.2231250711891969</v>
       </c>
       <c r="T21">
-        <v>1.493341384510321</v>
+        <v>1.518928209152212</v>
       </c>
       <c r="U21">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.1574305228605604</v>
+        <v>0.1273598241767621</v>
       </c>
       <c r="W21">
-        <v>0.1691879510095995</v>
+        <v>0.2057685534591195</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y21">
-        <v>0.5247684095352013</v>
+        <v>0.4245327472558736</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3047,22 +3047,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2196537676431814</v>
+        <v>0.2215537676431814</v>
       </c>
       <c r="C22">
-        <v>18.10286845077773</v>
+        <v>17.56319422570779</v>
       </c>
       <c r="D22">
-        <v>23.44686845077773</v>
+        <v>23.19339422570779</v>
       </c>
       <c r="E22">
-        <v>3.404</v>
+        <v>3.690200000000001</v>
       </c>
       <c r="F22">
-        <v>5.724</v>
+        <v>6.010200000000001</v>
       </c>
       <c r="G22">
         <v>0.38</v>
@@ -3083,37 +3083,37 @@
         <v>0.573</v>
       </c>
       <c r="M22">
-        <v>1.3497192</v>
+        <v>1.41720516</v>
       </c>
       <c r="N22">
-        <v>-0.7767192000000001</v>
+        <v>-0.8442051600000005</v>
       </c>
       <c r="O22">
-        <v>-0.23301576</v>
+        <v>-0.2532615480000001</v>
       </c>
       <c r="P22">
-        <v>-0.54370344</v>
+        <v>-0.5909436120000003</v>
       </c>
       <c r="Q22">
-        <v>-1.11670344</v>
+        <v>-1.163943612</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2231250711891969</v>
+        <v>0.2253696923434905</v>
       </c>
       <c r="T22">
-        <v>1.518928209152212</v>
+        <v>1.538155148508568</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.1273598241767621</v>
+        <v>0.1212950706445353</v>
       </c>
       <c r="W22">
-        <v>0.2057685534591195</v>
+        <v>0.2071986223420186</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.4245327472558736</v>
+        <v>0.404316902148451</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3129,22 +3129,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2215537676431814</v>
+        <v>0.2234537676431814</v>
       </c>
       <c r="C23">
-        <v>17.56319422570779</v>
+        <v>17.02894179420881</v>
       </c>
       <c r="D23">
-        <v>23.19339422570779</v>
+        <v>22.94534179420881</v>
       </c>
       <c r="E23">
-        <v>3.6902</v>
+        <v>3.9764</v>
       </c>
       <c r="F23">
-        <v>6.0102</v>
+        <v>6.2964</v>
       </c>
       <c r="G23">
         <v>0.38</v>
@@ -3165,37 +3165,37 @@
         <v>0.573</v>
       </c>
       <c r="M23">
-        <v>1.41720516</v>
+        <v>1.48469112</v>
       </c>
       <c r="N23">
-        <v>-0.8442051600000002</v>
+        <v>-0.9116911200000002</v>
       </c>
       <c r="O23">
-        <v>-0.2532615480000001</v>
+        <v>-0.273507336</v>
       </c>
       <c r="P23">
-        <v>-0.5909436120000002</v>
+        <v>-0.6381837840000002</v>
       </c>
       <c r="Q23">
-        <v>-1.163943612</v>
+        <v>-1.211183784</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2253696923434905</v>
+        <v>0.2276718678863558</v>
       </c>
       <c r="T23">
-        <v>1.538155148508568</v>
+        <v>1.55787508630996</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.1212950706445353</v>
+        <v>0.115781658342511</v>
       </c>
       <c r="W23">
-        <v>0.2071986223420186</v>
+        <v>0.2084986849628359</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.4043169021484511</v>
+        <v>0.3859388611417033</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3211,22 +3211,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2234537676431814</v>
+        <v>0.2253537676431814</v>
       </c>
       <c r="C24">
-        <v>17.02894179420881</v>
+        <v>16.49993903946165</v>
       </c>
       <c r="D24">
-        <v>22.94534179420881</v>
+        <v>22.70253903946165</v>
       </c>
       <c r="E24">
-        <v>3.9764</v>
+        <v>4.262600000000001</v>
       </c>
       <c r="F24">
-        <v>6.2964</v>
+        <v>6.5826</v>
       </c>
       <c r="G24">
         <v>0.38</v>
@@ -3247,37 +3247,37 @@
         <v>0.573</v>
       </c>
       <c r="M24">
-        <v>1.48469112</v>
+        <v>1.55217708</v>
       </c>
       <c r="N24">
-        <v>-0.9116911200000002</v>
+        <v>-0.9791770800000001</v>
       </c>
       <c r="O24">
-        <v>-0.273507336</v>
+        <v>-0.293753124</v>
       </c>
       <c r="P24">
-        <v>-0.6381837840000002</v>
+        <v>-0.6854239560000002</v>
       </c>
       <c r="Q24">
-        <v>-1.211183784</v>
+        <v>-1.258423956</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2276718678863558</v>
+        <v>0.2300338401965682</v>
       </c>
       <c r="T24">
-        <v>1.55787508630996</v>
+        <v>1.578107230288012</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.115781658342511</v>
+        <v>0.1107476731971844</v>
       </c>
       <c r="W24">
-        <v>0.2084986849628359</v>
+        <v>0.2096856986601039</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.3859388611417033</v>
+        <v>0.3691589106572813</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3293,22 +3293,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2253537676431814</v>
+        <v>0.2272537676431814</v>
       </c>
       <c r="C25">
-        <v>16.49993903946165</v>
+        <v>15.97602105357888</v>
       </c>
       <c r="D25">
-        <v>22.70253903946165</v>
+        <v>22.46482105357888</v>
       </c>
       <c r="E25">
-        <v>4.262600000000001</v>
+        <v>4.548800000000002</v>
       </c>
       <c r="F25">
-        <v>6.5826</v>
+        <v>6.868800000000001</v>
       </c>
       <c r="G25">
         <v>0.38</v>
@@ -3329,37 +3329,37 @@
         <v>0.573</v>
       </c>
       <c r="M25">
-        <v>1.55217708</v>
+        <v>1.61966304</v>
       </c>
       <c r="N25">
-        <v>-0.9791770800000001</v>
+        <v>-1.04666304</v>
       </c>
       <c r="O25">
-        <v>-0.293753124</v>
+        <v>-0.3139989120000001</v>
       </c>
       <c r="P25">
-        <v>-0.6854239560000002</v>
+        <v>-0.7326641280000002</v>
       </c>
       <c r="Q25">
-        <v>-1.258423956</v>
+        <v>-1.305664128</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2300338401965682</v>
+        <v>0.2324579696728388</v>
       </c>
       <c r="T25">
-        <v>1.578107230288012</v>
+        <v>1.598871799107591</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.1107476731971844</v>
+        <v>0.1061331868139684</v>
       </c>
       <c r="W25">
-        <v>0.2096856986601039</v>
+        <v>0.2107737945492663</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3691589106572813</v>
+        <v>0.3537772893798946</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3375,22 +3375,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2272537676431814</v>
+        <v>0.2291537676431814</v>
       </c>
       <c r="C26">
-        <v>15.97602105357888</v>
+        <v>15.45702976409273</v>
       </c>
       <c r="D26">
-        <v>22.46482105357888</v>
+        <v>22.23202976409273</v>
       </c>
       <c r="E26">
-        <v>4.5488</v>
+        <v>4.835000000000001</v>
       </c>
       <c r="F26">
-        <v>6.8688</v>
+        <v>7.155</v>
       </c>
       <c r="G26">
         <v>0.38</v>
@@ -3411,37 +3411,37 @@
         <v>0.573</v>
       </c>
       <c r="M26">
-        <v>1.61966304</v>
+        <v>1.687149</v>
       </c>
       <c r="N26">
-        <v>-1.04666304</v>
+        <v>-1.114149</v>
       </c>
       <c r="O26">
-        <v>-0.313998912</v>
+        <v>-0.3342447000000001</v>
       </c>
       <c r="P26">
-        <v>-0.7326641280000001</v>
+        <v>-0.7799043000000002</v>
       </c>
       <c r="Q26">
-        <v>-1.305664128</v>
+        <v>-1.3529043</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2324579696728388</v>
+        <v>0.23494674260181</v>
       </c>
       <c r="T26">
-        <v>1.598871799107591</v>
+        <v>1.620190089762359</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.1061331868139684</v>
+        <v>0.1018878593414097</v>
       </c>
       <c r="W26">
-        <v>0.2107737945492663</v>
+        <v>0.2117748427672956</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.3537772893798947</v>
+        <v>0.3396261978046988</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3457,22 +3457,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2291537676431814</v>
+        <v>0.2310537676431814</v>
       </c>
       <c r="C27">
-        <v>15.45702976409273</v>
+        <v>14.94281358342785</v>
       </c>
       <c r="D27">
-        <v>22.23202976409273</v>
+        <v>22.00401358342785</v>
       </c>
       <c r="E27">
-        <v>4.835000000000001</v>
+        <v>5.1212</v>
       </c>
       <c r="F27">
-        <v>7.155</v>
+        <v>7.4412</v>
       </c>
       <c r="G27">
         <v>0.38</v>
@@ -3493,37 +3493,37 @@
         <v>0.573</v>
       </c>
       <c r="M27">
-        <v>1.687149</v>
+        <v>1.75463496</v>
       </c>
       <c r="N27">
-        <v>-1.114149</v>
+        <v>-1.18163496</v>
       </c>
       <c r="O27">
-        <v>-0.3342447000000001</v>
+        <v>-0.354490488</v>
       </c>
       <c r="P27">
-        <v>-0.7799043000000002</v>
+        <v>-0.8271444720000002</v>
       </c>
       <c r="Q27">
-        <v>-1.3529043</v>
+        <v>-1.400144472</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.23494674260181</v>
+        <v>0.2375027796639967</v>
       </c>
       <c r="T27">
-        <v>1.620190089762359</v>
+        <v>1.642084550434823</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.1018878593414097</v>
+        <v>0.09796909552058622</v>
       </c>
       <c r="W27">
-        <v>0.2117748427672956</v>
+        <v>0.2126988872762458</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.3396261978046988</v>
+        <v>0.3265636517352873</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3539,22 +3539,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2310537676431814</v>
+        <v>0.2329537676431814</v>
       </c>
       <c r="C28">
-        <v>14.94281358342785</v>
+        <v>14.43322707972561</v>
       </c>
       <c r="D28">
-        <v>22.00401358342785</v>
+        <v>21.78062707972561</v>
       </c>
       <c r="E28">
-        <v>5.1212</v>
+        <v>5.407400000000001</v>
       </c>
       <c r="F28">
-        <v>7.4412</v>
+        <v>7.727400000000001</v>
       </c>
       <c r="G28">
         <v>0.38</v>
@@ -3575,37 +3575,37 @@
         <v>0.573</v>
       </c>
       <c r="M28">
-        <v>1.75463496</v>
+        <v>1.82212092</v>
       </c>
       <c r="N28">
-        <v>-1.18163496</v>
+        <v>-1.24912092</v>
       </c>
       <c r="O28">
-        <v>-0.354490488</v>
+        <v>-0.3747362760000001</v>
       </c>
       <c r="P28">
-        <v>-0.8271444720000002</v>
+        <v>-0.8743846440000003</v>
       </c>
       <c r="Q28">
-        <v>-1.400144472</v>
+        <v>-1.447384644</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2375027796639967</v>
+        <v>0.2401288451388459</v>
       </c>
       <c r="T28">
-        <v>1.642084550434823</v>
+        <v>1.664578859344889</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.09796909552058622</v>
+        <v>0.09434061050130522</v>
       </c>
       <c r="W28">
-        <v>0.2126988872762458</v>
+        <v>0.2135544840437922</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.3265636517352873</v>
+        <v>0.3144687016710175</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3621,22 +3621,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2329537676431814</v>
+        <v>0.2348537676431814</v>
       </c>
       <c r="C29">
-        <v>14.43322707972561</v>
+        <v>13.92813066751771</v>
       </c>
       <c r="D29">
-        <v>21.78062707972561</v>
+        <v>21.56173066751771</v>
       </c>
       <c r="E29">
-        <v>5.407400000000001</v>
+        <v>5.6936</v>
       </c>
       <c r="F29">
-        <v>7.727400000000001</v>
+        <v>8.0136</v>
       </c>
       <c r="G29">
         <v>0.38</v>
@@ -3657,37 +3657,37 @@
         <v>0.573</v>
       </c>
       <c r="M29">
-        <v>1.82212092</v>
+        <v>1.88960688</v>
       </c>
       <c r="N29">
-        <v>-1.24912092</v>
+        <v>-1.31660688</v>
       </c>
       <c r="O29">
-        <v>-0.3747362760000001</v>
+        <v>-0.394982064</v>
       </c>
       <c r="P29">
-        <v>-0.8743846440000003</v>
+        <v>-0.9216248160000001</v>
       </c>
       <c r="Q29">
-        <v>-1.447384644</v>
+        <v>-1.494624816</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2401288451388459</v>
+        <v>0.2428278568768854</v>
       </c>
       <c r="T29">
-        <v>1.664578859344889</v>
+        <v>1.687698010169124</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.09434061050130522</v>
+        <v>0.09097130298340148</v>
       </c>
       <c r="W29">
-        <v>0.2135544840437922</v>
+        <v>0.2143489667565139</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3144687016710175</v>
+        <v>0.3032376766113383</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3703,22 +3703,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2348537676431814</v>
+        <v>0.2367537676431814</v>
       </c>
       <c r="C30">
-        <v>13.92813066751771</v>
+        <v>13.42739031686678</v>
       </c>
       <c r="D30">
-        <v>21.56173066751771</v>
+        <v>21.34719031686679</v>
       </c>
       <c r="E30">
-        <v>5.6936</v>
+        <v>5.979800000000001</v>
       </c>
       <c r="F30">
-        <v>8.0136</v>
+        <v>8.299800000000001</v>
       </c>
       <c r="G30">
         <v>0.38</v>
@@ -3739,37 +3739,37 @@
         <v>0.573</v>
       </c>
       <c r="M30">
-        <v>1.88960688</v>
+        <v>1.95709284</v>
       </c>
       <c r="N30">
-        <v>-1.31660688</v>
+        <v>-1.38409284</v>
       </c>
       <c r="O30">
-        <v>-0.394982064</v>
+        <v>-0.4152278520000001</v>
       </c>
       <c r="P30">
-        <v>-0.9216248160000001</v>
+        <v>-0.9688649880000002</v>
       </c>
       <c r="Q30">
-        <v>-1.494624816</v>
+        <v>-1.541864988</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2428278568768854</v>
+        <v>0.245602897114588</v>
       </c>
       <c r="T30">
-        <v>1.687698010169124</v>
+        <v>1.711468404678548</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.09097130298340148</v>
+        <v>0.08783436150121522</v>
       </c>
       <c r="W30">
-        <v>0.2143489667565139</v>
+        <v>0.2150886575580135</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3032376766113383</v>
+        <v>0.2927812050040507</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3785,22 +3785,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2367537676431814</v>
+        <v>0.2386537676431814</v>
       </c>
       <c r="C31">
-        <v>13.42739031686679</v>
+        <v>12.93087727970025</v>
       </c>
       <c r="D31">
-        <v>21.34719031686679</v>
+        <v>21.13687727970025</v>
       </c>
       <c r="E31">
-        <v>5.979799999999999</v>
+        <v>6.266</v>
       </c>
       <c r="F31">
-        <v>8.299799999999999</v>
+        <v>8.586</v>
       </c>
       <c r="G31">
         <v>0.38</v>
@@ -3821,37 +3821,37 @@
         <v>0.573</v>
       </c>
       <c r="M31">
-        <v>1.95709284</v>
+        <v>2.0245788</v>
       </c>
       <c r="N31">
-        <v>-1.38409284</v>
+        <v>-1.4515788</v>
       </c>
       <c r="O31">
-        <v>-0.415227852</v>
+        <v>-0.43547364</v>
       </c>
       <c r="P31">
-        <v>-0.968864988</v>
+        <v>-1.01610516</v>
       </c>
       <c r="Q31">
-        <v>-1.541864988</v>
+        <v>-1.58910516</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.245602897114588</v>
+        <v>0.248457224216225</v>
       </c>
       <c r="T31">
-        <v>1.711468404678548</v>
+        <v>1.735917953316813</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.08783436150121524</v>
+        <v>0.08490654945117472</v>
       </c>
       <c r="W31">
-        <v>0.2150886575580135</v>
+        <v>0.215779035639413</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2927812050040508</v>
+        <v>0.2830218315039158</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3867,22 +3867,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2386537676431814</v>
+        <v>0.2405537676431814</v>
       </c>
       <c r="C32">
-        <v>12.93087727970025</v>
+        <v>12.43846783216335</v>
       </c>
       <c r="D32">
-        <v>21.13687727970025</v>
+        <v>20.93066783216335</v>
       </c>
       <c r="E32">
-        <v>6.266</v>
+        <v>6.552199999999999</v>
       </c>
       <c r="F32">
-        <v>8.586</v>
+        <v>8.872199999999999</v>
       </c>
       <c r="G32">
         <v>0.38</v>
@@ -3903,37 +3903,37 @@
         <v>0.573</v>
       </c>
       <c r="M32">
-        <v>2.0245788</v>
+        <v>2.09206476</v>
       </c>
       <c r="N32">
-        <v>-1.4515788</v>
+        <v>-1.51906476</v>
       </c>
       <c r="O32">
-        <v>-0.43547364</v>
+        <v>-0.455719428</v>
       </c>
       <c r="P32">
-        <v>-1.01610516</v>
+        <v>-1.063345332</v>
       </c>
       <c r="Q32">
-        <v>-1.58910516</v>
+        <v>-1.636345332</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.248457224216225</v>
+        <v>0.25139428543675</v>
       </c>
       <c r="T32">
-        <v>1.735917953316813</v>
+        <v>1.761076184524303</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.08490654945117472</v>
+        <v>0.08216762850113683</v>
       </c>
       <c r="W32">
-        <v>0.215779035639413</v>
+        <v>0.216424873199432</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2830218315039158</v>
+        <v>0.2738920950037894</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3949,22 +3949,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2405537676431814</v>
+        <v>0.2424537676431814</v>
       </c>
       <c r="C33">
-        <v>12.43846783216335</v>
+        <v>11.95004303190797</v>
       </c>
       <c r="D33">
-        <v>20.93066783216335</v>
+        <v>20.72844303190797</v>
       </c>
       <c r="E33">
-        <v>6.552199999999999</v>
+        <v>6.8384</v>
       </c>
       <c r="F33">
-        <v>8.872199999999999</v>
+        <v>9.1584</v>
       </c>
       <c r="G33">
         <v>0.38</v>
@@ -3985,37 +3985,37 @@
         <v>0.573</v>
       </c>
       <c r="M33">
-        <v>2.09206476</v>
+        <v>2.15955072</v>
       </c>
       <c r="N33">
-        <v>-1.51906476</v>
+        <v>-1.58655072</v>
       </c>
       <c r="O33">
-        <v>-0.455719428</v>
+        <v>-0.4759652160000001</v>
       </c>
       <c r="P33">
-        <v>-1.063345332</v>
+        <v>-1.110585504</v>
       </c>
       <c r="Q33">
-        <v>-1.636345332</v>
+        <v>-1.683585504</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.25139428543675</v>
+        <v>0.2544177308108199</v>
       </c>
       <c r="T33">
-        <v>1.761076184524303</v>
+        <v>1.786974363708484</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.08216762850113683</v>
+        <v>0.07959989011047629</v>
       </c>
       <c r="W33">
-        <v>0.216424873199432</v>
+        <v>0.2170303459119497</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2738920950037894</v>
+        <v>0.2653329670349209</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2424537676431814</v>
+        <v>0.2443537676431814</v>
       </c>
       <c r="C34">
-        <v>11.95004303190797</v>
+        <v>11.46548848931675</v>
       </c>
       <c r="D34">
-        <v>20.72844303190797</v>
+        <v>20.53008848931676</v>
       </c>
       <c r="E34">
-        <v>6.8384</v>
+        <v>7.124600000000001</v>
       </c>
       <c r="F34">
-        <v>9.1584</v>
+        <v>9.444600000000001</v>
       </c>
       <c r="G34">
         <v>0.38</v>
@@ -4067,37 +4067,37 @@
         <v>0.573</v>
       </c>
       <c r="M34">
-        <v>2.15955072</v>
+        <v>2.22703668</v>
       </c>
       <c r="N34">
-        <v>-1.58655072</v>
+        <v>-1.65403668</v>
       </c>
       <c r="O34">
-        <v>-0.4759652160000001</v>
+        <v>-0.4962110040000001</v>
       </c>
       <c r="P34">
-        <v>-1.110585504</v>
+        <v>-1.157825676</v>
       </c>
       <c r="Q34">
-        <v>-1.683585504</v>
+        <v>-1.730825676</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2544177308108199</v>
+        <v>0.2575314282856082</v>
       </c>
       <c r="T34">
-        <v>1.786974363708484</v>
+        <v>1.813645622868312</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.07959989011047629</v>
+        <v>0.07718777222834064</v>
       </c>
       <c r="W34">
-        <v>0.2170303459119497</v>
+        <v>0.2175991233085573</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2653329670349209</v>
+        <v>0.2572925740944688</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4113,22 +4113,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2443537676431814</v>
+        <v>0.2462537676431814</v>
       </c>
       <c r="C35">
-        <v>11.46548848931675</v>
+        <v>10.98469415173795</v>
       </c>
       <c r="D35">
-        <v>20.53008848931676</v>
+        <v>20.33549415173795</v>
       </c>
       <c r="E35">
-        <v>7.124600000000001</v>
+        <v>7.4108</v>
       </c>
       <c r="F35">
-        <v>9.444600000000001</v>
+        <v>9.7308</v>
       </c>
       <c r="G35">
         <v>0.38</v>
@@ -4149,37 +4149,37 @@
         <v>0.573</v>
       </c>
       <c r="M35">
-        <v>2.22703668</v>
+        <v>2.29452264</v>
       </c>
       <c r="N35">
-        <v>-1.65403668</v>
+        <v>-1.72152264</v>
       </c>
       <c r="O35">
-        <v>-0.4962110040000001</v>
+        <v>-0.5164567920000001</v>
       </c>
       <c r="P35">
-        <v>-1.157825676</v>
+        <v>-1.205065848</v>
       </c>
       <c r="Q35">
-        <v>-1.730825676</v>
+        <v>-1.778065848</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2575314282856082</v>
+        <v>0.2607394802293295</v>
       </c>
       <c r="T35">
-        <v>1.813645622868312</v>
+        <v>1.841125102002681</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.07718777222834064</v>
+        <v>0.07491754363338946</v>
       </c>
       <c r="W35">
-        <v>0.2175991233085573</v>
+        <v>0.2181344432112468</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2572925740944688</v>
+        <v>0.2497251454446315</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4195,22 +4195,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2462537676431814</v>
+        <v>0.2481537676431813</v>
       </c>
       <c r="C36">
-        <v>10.98469415173795</v>
+        <v>10.50755409987574</v>
       </c>
       <c r="D36">
-        <v>20.33549415173795</v>
+        <v>20.14455409987574</v>
       </c>
       <c r="E36">
-        <v>7.4108</v>
+        <v>7.697000000000001</v>
       </c>
       <c r="F36">
-        <v>9.7308</v>
+        <v>10.017</v>
       </c>
       <c r="G36">
         <v>0.38</v>
@@ -4231,37 +4231,37 @@
         <v>0.573</v>
       </c>
       <c r="M36">
-        <v>2.29452264</v>
+        <v>2.3620086</v>
       </c>
       <c r="N36">
-        <v>-1.72152264</v>
+        <v>-1.7890086</v>
       </c>
       <c r="O36">
-        <v>-0.5164567920000001</v>
+        <v>-0.53670258</v>
       </c>
       <c r="P36">
-        <v>-1.205065848</v>
+        <v>-1.25230602</v>
       </c>
       <c r="Q36">
-        <v>-1.778065848</v>
+        <v>-1.82530602</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2607394802293295</v>
+        <v>0.2640462414636269</v>
       </c>
       <c r="T36">
-        <v>1.841125102002681</v>
+        <v>1.869450103571952</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.07491754363338946</v>
+        <v>0.07277704238672118</v>
       </c>
       <c r="W36">
-        <v>0.2181344432112468</v>
+        <v>0.2186391734052111</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2497251454446315</v>
+        <v>0.2425901412890706</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4277,22 +4277,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2481537676431813</v>
+        <v>0.2500537676431814</v>
       </c>
       <c r="C37">
-        <v>10.50755409987574</v>
+        <v>10.03396635554474</v>
       </c>
       <c r="D37">
-        <v>20.14455409987574</v>
+        <v>19.95716635554474</v>
       </c>
       <c r="E37">
-        <v>7.697000000000001</v>
+        <v>7.983200000000002</v>
       </c>
       <c r="F37">
-        <v>10.017</v>
+        <v>10.3032</v>
       </c>
       <c r="G37">
         <v>0.38</v>
@@ -4313,37 +4313,37 @@
         <v>0.573</v>
       </c>
       <c r="M37">
-        <v>2.3620086</v>
+        <v>2.429494560000001</v>
       </c>
       <c r="N37">
-        <v>-1.7890086</v>
+        <v>-1.856494560000001</v>
       </c>
       <c r="O37">
-        <v>-0.53670258</v>
+        <v>-0.5569483680000001</v>
       </c>
       <c r="P37">
-        <v>-1.25230602</v>
+        <v>-1.299546192000001</v>
       </c>
       <c r="Q37">
-        <v>-1.82530602</v>
+        <v>-1.872546192000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2640462414636269</v>
+        <v>0.2674563389864961</v>
       </c>
       <c r="T37">
-        <v>1.869450103571952</v>
+        <v>1.898660261440265</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.07277704238672118</v>
+        <v>0.07075545787597891</v>
       </c>
       <c r="W37">
-        <v>0.2186391734052111</v>
+        <v>0.2191158630328442</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2425901412890706</v>
+        <v>0.2358515262532631</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4359,22 +4359,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2500537676431814</v>
+        <v>0.2519537676431814</v>
       </c>
       <c r="C38">
-        <v>10.03396635554473</v>
+        <v>9.563832700055277</v>
       </c>
       <c r="D38">
-        <v>19.95716635554473</v>
+        <v>19.77323270005528</v>
       </c>
       <c r="E38">
-        <v>7.9832</v>
+        <v>8.269399999999999</v>
       </c>
       <c r="F38">
-        <v>10.3032</v>
+        <v>10.5894</v>
       </c>
       <c r="G38">
         <v>0.38</v>
@@ -4395,37 +4395,37 @@
         <v>0.573</v>
       </c>
       <c r="M38">
-        <v>2.42949456</v>
+        <v>2.49698052</v>
       </c>
       <c r="N38">
-        <v>-1.85649456</v>
+        <v>-1.92398052</v>
       </c>
       <c r="O38">
-        <v>-0.556948368</v>
+        <v>-0.577194156</v>
       </c>
       <c r="P38">
-        <v>-1.299546192</v>
+        <v>-1.346786364</v>
       </c>
       <c r="Q38">
-        <v>-1.872546192</v>
+        <v>-1.919786364</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2674563389864961</v>
+        <v>0.2709746935735833</v>
       </c>
       <c r="T38">
-        <v>1.898660261440265</v>
+        <v>1.92879772590757</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.07075545787597894</v>
+        <v>0.06884314820365518</v>
       </c>
       <c r="W38">
-        <v>0.2191158630328442</v>
+        <v>0.2195667856535781</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2358515262532631</v>
+        <v>0.2294771606788506</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4441,22 +4441,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2519537676431814</v>
+        <v>0.2538537676431813</v>
       </c>
       <c r="C39">
-        <v>9.563832700055277</v>
+        <v>9.097058502550061</v>
       </c>
       <c r="D39">
-        <v>19.77323270005528</v>
+        <v>19.59265850255006</v>
       </c>
       <c r="E39">
-        <v>8.269399999999999</v>
+        <v>8.5556</v>
       </c>
       <c r="F39">
-        <v>10.5894</v>
+        <v>10.8756</v>
       </c>
       <c r="G39">
         <v>0.38</v>
@@ -4477,37 +4477,37 @@
         <v>0.573</v>
       </c>
       <c r="M39">
-        <v>2.49698052</v>
+        <v>2.56446648</v>
       </c>
       <c r="N39">
-        <v>-1.92398052</v>
+        <v>-1.99146648</v>
       </c>
       <c r="O39">
-        <v>-0.577194156</v>
+        <v>-0.597439944</v>
       </c>
       <c r="P39">
-        <v>-1.346786364</v>
+        <v>-1.394026536</v>
       </c>
       <c r="Q39">
-        <v>-1.919786364</v>
+        <v>-1.967026536</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2709746935735833</v>
+        <v>0.2746065434699314</v>
       </c>
       <c r="T39">
-        <v>1.92879772590757</v>
+        <v>1.959907366648015</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.06884314820365518</v>
+        <v>0.06703148640882214</v>
       </c>
       <c r="W39">
-        <v>0.2195667856535781</v>
+        <v>0.2199939755047997</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2294771606788506</v>
+        <v>0.2234382880294071</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4523,22 +4523,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2538537676431813</v>
+        <v>0.2557537676431814</v>
       </c>
       <c r="C40">
-        <v>9.097058502550061</v>
+        <v>8.6335525576617</v>
       </c>
       <c r="D40">
-        <v>19.59265850255006</v>
+        <v>19.4153525576617</v>
       </c>
       <c r="E40">
-        <v>8.5556</v>
+        <v>8.841800000000001</v>
       </c>
       <c r="F40">
-        <v>10.8756</v>
+        <v>11.1618</v>
       </c>
       <c r="G40">
         <v>0.38</v>
@@ -4559,37 +4559,37 @@
         <v>0.573</v>
       </c>
       <c r="M40">
-        <v>2.56446648</v>
+        <v>2.631952440000001</v>
       </c>
       <c r="N40">
-        <v>-1.99146648</v>
+        <v>-2.058952440000001</v>
       </c>
       <c r="O40">
-        <v>-0.597439944</v>
+        <v>-0.6176857320000001</v>
       </c>
       <c r="P40">
-        <v>-1.394026536</v>
+        <v>-1.441266708000001</v>
       </c>
       <c r="Q40">
-        <v>-1.967026536</v>
+        <v>-2.014266708000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2746065434699314</v>
+        <v>0.2783574704120614</v>
       </c>
       <c r="T40">
-        <v>1.959907366648015</v>
+        <v>1.992036995609457</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.06703148640882214</v>
+        <v>0.06531273034705747</v>
       </c>
       <c r="W40">
-        <v>0.2199939755047997</v>
+        <v>0.2203992581841639</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2234382880294071</v>
+        <v>0.2177091011568583</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4605,22 +4605,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2557537676431814</v>
+        <v>0.2576537676431814</v>
       </c>
       <c r="C41">
-        <v>8.6335525576617</v>
+        <v>8.173226931906068</v>
       </c>
       <c r="D41">
-        <v>19.4153525576617</v>
+        <v>19.24122693190607</v>
       </c>
       <c r="E41">
-        <v>8.841800000000001</v>
+        <v>9.128</v>
       </c>
       <c r="F41">
-        <v>11.1618</v>
+        <v>11.448</v>
       </c>
       <c r="G41">
         <v>0.38</v>
@@ -4641,37 +4641,37 @@
         <v>0.573</v>
       </c>
       <c r="M41">
-        <v>2.631952440000001</v>
+        <v>2.6994384</v>
       </c>
       <c r="N41">
-        <v>-2.058952440000001</v>
+        <v>-2.1264384</v>
       </c>
       <c r="O41">
-        <v>-0.6176857320000001</v>
+        <v>-0.63793152</v>
       </c>
       <c r="P41">
-        <v>-1.441266708000001</v>
+        <v>-1.48850688</v>
       </c>
       <c r="Q41">
-        <v>-2.014266708000001</v>
+        <v>-2.06150688</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2783574704120614</v>
+        <v>0.2822334282522625</v>
       </c>
       <c r="T41">
-        <v>1.992036995609457</v>
+        <v>2.025237612202949</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.06531273034705747</v>
+        <v>0.06367991208838104</v>
       </c>
       <c r="W41">
-        <v>0.2203992581841639</v>
+        <v>0.2207842767295597</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2177091011568583</v>
+        <v>0.2122663736279368</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4687,22 +4687,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2576537676431814</v>
+        <v>0.2595537676431814</v>
       </c>
       <c r="C42">
-        <v>8.173226931906068</v>
+        <v>7.715996818267797</v>
       </c>
       <c r="D42">
-        <v>19.24122693190607</v>
+        <v>19.0701968182678</v>
       </c>
       <c r="E42">
-        <v>9.128</v>
+        <v>9.414200000000001</v>
       </c>
       <c r="F42">
-        <v>11.448</v>
+        <v>11.7342</v>
       </c>
       <c r="G42">
         <v>0.38</v>
@@ -4723,37 +4723,37 @@
         <v>0.573</v>
       </c>
       <c r="M42">
-        <v>2.6994384</v>
+        <v>2.76692436</v>
       </c>
       <c r="N42">
-        <v>-2.1264384</v>
+        <v>-2.19392436</v>
       </c>
       <c r="O42">
-        <v>-0.63793152</v>
+        <v>-0.6581773080000001</v>
       </c>
       <c r="P42">
-        <v>-1.48850688</v>
+        <v>-1.535747052000001</v>
       </c>
       <c r="Q42">
-        <v>-2.06150688</v>
+        <v>-2.108747052</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2822334282522625</v>
+        <v>0.2862407744938262</v>
       </c>
       <c r="T42">
-        <v>2.025237612202949</v>
+        <v>2.059563673426727</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.06367991208838104</v>
+        <v>0.06212674350085955</v>
       </c>
       <c r="W42">
-        <v>0.2207842767295597</v>
+        <v>0.2211505138824973</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2122663736279368</v>
+        <v>0.2070891450028651</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4769,22 +4769,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2595537676431814</v>
+        <v>0.2614537676431814</v>
       </c>
       <c r="C43">
-        <v>7.715996818267797</v>
+        <v>7.261780398472798</v>
       </c>
       <c r="D43">
-        <v>19.0701968182678</v>
+        <v>18.9021803984728</v>
       </c>
       <c r="E43">
-        <v>9.414200000000001</v>
+        <v>9.700400000000002</v>
       </c>
       <c r="F43">
-        <v>11.7342</v>
+        <v>12.0204</v>
       </c>
       <c r="G43">
         <v>0.38</v>
@@ -4805,37 +4805,37 @@
         <v>0.573</v>
       </c>
       <c r="M43">
-        <v>2.76692436</v>
+        <v>2.834410320000001</v>
       </c>
       <c r="N43">
-        <v>-2.19392436</v>
+        <v>-2.261410320000001</v>
       </c>
       <c r="O43">
-        <v>-0.6581773080000001</v>
+        <v>-0.6784230960000003</v>
       </c>
       <c r="P43">
-        <v>-1.535747052000001</v>
+        <v>-1.582987224</v>
       </c>
       <c r="Q43">
-        <v>-2.108747052</v>
+        <v>-2.155987224</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2862407744938262</v>
+        <v>0.2903863050885474</v>
       </c>
       <c r="T43">
-        <v>2.059563673426727</v>
+        <v>2.095073391934085</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.06212674350085955</v>
+        <v>0.06064753532226764</v>
       </c>
       <c r="W43">
-        <v>0.2211505138824973</v>
+        <v>0.2214993111710093</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2070891450028651</v>
+        <v>0.2021584510742255</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4851,22 +4851,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2614537676431814</v>
+        <v>0.2633537676431814</v>
       </c>
       <c r="C44">
-        <v>7.2617803984728</v>
+        <v>6.810498712477813</v>
       </c>
       <c r="D44">
-        <v>18.9021803984728</v>
+        <v>18.73709871247781</v>
       </c>
       <c r="E44">
-        <v>9.7004</v>
+        <v>9.986599999999999</v>
       </c>
       <c r="F44">
-        <v>12.0204</v>
+        <v>12.3066</v>
       </c>
       <c r="G44">
         <v>0.38</v>
@@ -4887,37 +4887,37 @@
         <v>0.573</v>
       </c>
       <c r="M44">
-        <v>2.83441032</v>
+        <v>2.90189628</v>
       </c>
       <c r="N44">
-        <v>-2.26141032</v>
+        <v>-2.32889628</v>
       </c>
       <c r="O44">
-        <v>-0.6784230960000001</v>
+        <v>-0.6986688839999999</v>
       </c>
       <c r="P44">
-        <v>-1.582987224</v>
+        <v>-1.630227396</v>
       </c>
       <c r="Q44">
-        <v>-2.155987224</v>
+        <v>-2.203227396</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2903863050885473</v>
+        <v>0.2946772928971184</v>
       </c>
       <c r="T44">
-        <v>2.095073391934084</v>
+        <v>2.131829065476788</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06064753532226765</v>
+        <v>0.05923712752407539</v>
       </c>
       <c r="W44">
-        <v>0.2214993111710093</v>
+        <v>0.221831885329823</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2021584510742255</v>
+        <v>0.1974570917469179</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4933,22 +4933,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2633537676431814</v>
+        <v>0.2652537676431814</v>
       </c>
       <c r="C45">
-        <v>6.810498712477813</v>
+        <v>6.362075534739564</v>
       </c>
       <c r="D45">
-        <v>18.73709871247781</v>
+        <v>18.57487553473957</v>
       </c>
       <c r="E45">
-        <v>9.986599999999999</v>
+        <v>10.2728</v>
       </c>
       <c r="F45">
-        <v>12.3066</v>
+        <v>12.5928</v>
       </c>
       <c r="G45">
         <v>0.38</v>
@@ -4969,37 +4969,37 @@
         <v>0.573</v>
       </c>
       <c r="M45">
-        <v>2.90189628</v>
+        <v>2.96938224</v>
       </c>
       <c r="N45">
-        <v>-2.32889628</v>
+        <v>-2.39638224</v>
       </c>
       <c r="O45">
-        <v>-0.6986688839999999</v>
+        <v>-0.718914672</v>
       </c>
       <c r="P45">
-        <v>-1.630227396</v>
+        <v>-1.677467568</v>
       </c>
       <c r="Q45">
-        <v>-2.203227396</v>
+        <v>-2.250467568</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2946772928971184</v>
+        <v>0.2991215302702813</v>
       </c>
       <c r="T45">
-        <v>2.131829065476788</v>
+        <v>2.169897441646016</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.05923712752407539</v>
+        <v>0.05789082917125549</v>
       </c>
       <c r="W45">
-        <v>0.221831885329823</v>
+        <v>0.222149342481418</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1974570917469179</v>
+        <v>0.1929694305708516</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5015,22 +5015,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2652537676431814</v>
+        <v>0.2671537676431814</v>
       </c>
       <c r="C46">
-        <v>6.362075534739564</v>
+        <v>5.916437256856277</v>
       </c>
       <c r="D46">
-        <v>18.57487553473957</v>
+        <v>18.41543725685628</v>
       </c>
       <c r="E46">
-        <v>10.2728</v>
+        <v>10.559</v>
       </c>
       <c r="F46">
-        <v>12.5928</v>
+        <v>12.879</v>
       </c>
       <c r="G46">
         <v>0.38</v>
@@ -5051,37 +5051,37 @@
         <v>0.573</v>
       </c>
       <c r="M46">
-        <v>2.96938224</v>
+        <v>3.0368682</v>
       </c>
       <c r="N46">
-        <v>-2.39638224</v>
+        <v>-2.4638682</v>
       </c>
       <c r="O46">
-        <v>-0.718914672</v>
+        <v>-0.73916046</v>
       </c>
       <c r="P46">
-        <v>-1.677467568</v>
+        <v>-1.72470774</v>
       </c>
       <c r="Q46">
-        <v>-2.250467568</v>
+        <v>-2.29770774</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2991215302702813</v>
+        <v>0.3037273762751955</v>
       </c>
       <c r="T46">
-        <v>2.169897441646016</v>
+        <v>2.209350122403217</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.05789082917125549</v>
+        <v>0.05660436630078314</v>
       </c>
       <c r="W46">
-        <v>0.222149342481418</v>
+        <v>0.2224526904262754</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1929694305708516</v>
+        <v>0.1886812210026105</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2671537676431814</v>
+        <v>0.2690537676431815</v>
       </c>
       <c r="C47">
-        <v>5.916437256856277</v>
+        <v>5.473512776201828</v>
       </c>
       <c r="D47">
-        <v>18.41543725685628</v>
+        <v>18.25871277620183</v>
       </c>
       <c r="E47">
-        <v>10.559</v>
+        <v>10.8452</v>
       </c>
       <c r="F47">
-        <v>12.879</v>
+        <v>13.1652</v>
       </c>
       <c r="G47">
         <v>0.38</v>
@@ -5133,37 +5133,37 @@
         <v>0.573</v>
       </c>
       <c r="M47">
-        <v>3.0368682</v>
+        <v>3.10435416</v>
       </c>
       <c r="N47">
-        <v>-2.4638682</v>
+        <v>-2.53135416</v>
       </c>
       <c r="O47">
-        <v>-0.73916046</v>
+        <v>-0.759406248</v>
       </c>
       <c r="P47">
-        <v>-1.72470774</v>
+        <v>-1.771947912</v>
       </c>
       <c r="Q47">
-        <v>-2.29770774</v>
+        <v>-2.344947912</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3037273762751955</v>
+        <v>0.3085038091691806</v>
       </c>
       <c r="T47">
-        <v>2.209350122403217</v>
+        <v>2.250264013558832</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.05660436630078314</v>
+        <v>0.05537383659859221</v>
       </c>
       <c r="W47">
-        <v>0.2224526904262754</v>
+        <v>0.222742849330052</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1886812210026105</v>
+        <v>0.1845794553286407</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5179,22 +5179,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2690537676431815</v>
+        <v>0.2709537676431815</v>
       </c>
       <c r="C48">
-        <v>5.473512776201828</v>
+        <v>5.033233390198562</v>
       </c>
       <c r="D48">
-        <v>18.25871277620183</v>
+        <v>18.10463339019856</v>
       </c>
       <c r="E48">
-        <v>10.8452</v>
+        <v>11.1314</v>
       </c>
       <c r="F48">
-        <v>13.1652</v>
+        <v>13.4514</v>
       </c>
       <c r="G48">
         <v>0.38</v>
@@ -5215,37 +5215,37 @@
         <v>0.573</v>
       </c>
       <c r="M48">
-        <v>3.10435416</v>
+        <v>3.171840120000001</v>
       </c>
       <c r="N48">
-        <v>-2.53135416</v>
+        <v>-2.598840120000001</v>
       </c>
       <c r="O48">
-        <v>-0.759406248</v>
+        <v>-0.7796520360000002</v>
       </c>
       <c r="P48">
-        <v>-1.771947912</v>
+        <v>-1.819188084</v>
       </c>
       <c r="Q48">
-        <v>-2.344947912</v>
+        <v>-2.392188084</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3085038091691806</v>
+        <v>0.3134604848138821</v>
       </c>
       <c r="T48">
-        <v>2.250264013558832</v>
+        <v>2.292721825135414</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.05537383659859221</v>
+        <v>0.05419566986245194</v>
       </c>
       <c r="W48">
-        <v>0.222742849330052</v>
+        <v>0.2230206610464338</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1845794553286407</v>
+        <v>0.1806522328748398</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5261,22 +5261,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2709537676431815</v>
+        <v>0.2728537676431815</v>
       </c>
       <c r="C49">
-        <v>5.033233390198562</v>
+        <v>4.595532695898539</v>
       </c>
       <c r="D49">
-        <v>18.10463339019856</v>
+        <v>17.95313269589854</v>
       </c>
       <c r="E49">
-        <v>11.1314</v>
+        <v>11.4176</v>
       </c>
       <c r="F49">
-        <v>13.4514</v>
+        <v>13.7376</v>
       </c>
       <c r="G49">
         <v>0.38</v>
@@ -5297,37 +5297,37 @@
         <v>0.573</v>
       </c>
       <c r="M49">
-        <v>3.171840120000001</v>
+        <v>3.239326080000001</v>
       </c>
       <c r="N49">
-        <v>-2.598840120000001</v>
+        <v>-2.666326080000001</v>
       </c>
       <c r="O49">
-        <v>-0.7796520360000002</v>
+        <v>-0.7998978240000002</v>
       </c>
       <c r="P49">
-        <v>-1.819188084</v>
+        <v>-1.866428256</v>
       </c>
       <c r="Q49">
-        <v>-2.392188084</v>
+        <v>-2.439428256</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3134604848138821</v>
+        <v>0.3186078018295337</v>
       </c>
       <c r="T49">
-        <v>2.292721825135414</v>
+        <v>2.336812629464941</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.05419566986245194</v>
+        <v>0.05306659340698419</v>
       </c>
       <c r="W49">
-        <v>0.2230206610464338</v>
+        <v>0.2232868972746331</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1806522328748398</v>
+        <v>0.1768886446899474</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5343,22 +5343,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2728537676431814</v>
+        <v>0.2747537676431814</v>
       </c>
       <c r="C50">
-        <v>4.595532695898552</v>
+        <v>4.160346494564797</v>
       </c>
       <c r="D50">
-        <v>17.95313269589855</v>
+        <v>17.8041464945648</v>
       </c>
       <c r="E50">
-        <v>11.4176</v>
+        <v>11.7038</v>
       </c>
       <c r="F50">
-        <v>13.7376</v>
+        <v>14.0238</v>
       </c>
       <c r="G50">
         <v>0.38</v>
@@ -5379,37 +5379,37 @@
         <v>0.573</v>
       </c>
       <c r="M50">
-        <v>3.23932608</v>
+        <v>3.30681204</v>
       </c>
       <c r="N50">
-        <v>-2.66632608</v>
+        <v>-2.73381204</v>
       </c>
       <c r="O50">
-        <v>-0.799897824</v>
+        <v>-0.820143612</v>
       </c>
       <c r="P50">
-        <v>-1.866428256</v>
+        <v>-1.913668428</v>
       </c>
       <c r="Q50">
-        <v>-2.439428256</v>
+        <v>-2.486668428</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3186078018295336</v>
+        <v>0.3239569744144265</v>
       </c>
       <c r="T50">
-        <v>2.33681262946494</v>
+        <v>2.382632484944645</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0530665934069842</v>
+        <v>0.05198360170480085</v>
       </c>
       <c r="W50">
-        <v>0.2232868972746331</v>
+        <v>0.223542266718008</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1768886446899474</v>
+        <v>0.1732786723493361</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5425,22 +5425,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2747537676431814</v>
+        <v>0.2766537676431814</v>
       </c>
       <c r="C51">
-        <v>4.160346494564797</v>
+        <v>3.727612700964519</v>
       </c>
       <c r="D51">
-        <v>17.8041464945648</v>
+        <v>17.65761270096452</v>
       </c>
       <c r="E51">
-        <v>11.7038</v>
+        <v>11.99</v>
       </c>
       <c r="F51">
-        <v>14.0238</v>
+        <v>14.31</v>
       </c>
       <c r="G51">
         <v>0.38</v>
@@ -5461,37 +5461,37 @@
         <v>0.573</v>
       </c>
       <c r="M51">
-        <v>3.30681204</v>
+        <v>3.374298</v>
       </c>
       <c r="N51">
-        <v>-2.73381204</v>
+        <v>-2.801298000000001</v>
       </c>
       <c r="O51">
-        <v>-0.820143612</v>
+        <v>-0.8403894000000002</v>
       </c>
       <c r="P51">
-        <v>-1.913668428</v>
+        <v>-1.9609086</v>
       </c>
       <c r="Q51">
-        <v>-2.486668428</v>
+        <v>-2.5339086</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3239569744144265</v>
+        <v>0.329520113902715</v>
       </c>
       <c r="T51">
-        <v>2.382632484944645</v>
+        <v>2.430285134643538</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05198360170480085</v>
+        <v>0.05094392967070483</v>
       </c>
       <c r="W51">
-        <v>0.223542266718008</v>
+        <v>0.2237874213836478</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1732786723493361</v>
+        <v>0.1698130989023494</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5507,22 +5507,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2766537676431814</v>
+        <v>0.2785537676431814</v>
       </c>
       <c r="C52">
-        <v>3.727612700964519</v>
+        <v>3.29727125710499</v>
       </c>
       <c r="D52">
-        <v>17.65761270096452</v>
+        <v>17.51347125710499</v>
       </c>
       <c r="E52">
-        <v>11.99</v>
+        <v>12.2762</v>
       </c>
       <c r="F52">
-        <v>14.31</v>
+        <v>14.5962</v>
       </c>
       <c r="G52">
         <v>0.38</v>
@@ -5543,37 +5543,37 @@
         <v>0.573</v>
       </c>
       <c r="M52">
-        <v>3.374298</v>
+        <v>3.44178396</v>
       </c>
       <c r="N52">
-        <v>-2.801298000000001</v>
+        <v>-2.86878396</v>
       </c>
       <c r="O52">
-        <v>-0.8403894000000002</v>
+        <v>-0.8606351880000002</v>
       </c>
       <c r="P52">
-        <v>-1.9609086</v>
+        <v>-2.008148772</v>
       </c>
       <c r="Q52">
-        <v>-2.5339086</v>
+        <v>-2.581148772</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.329520113902715</v>
+        <v>0.3353103203088929</v>
       </c>
       <c r="T52">
-        <v>2.430285134643538</v>
+        <v>2.47988279045259</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05094392967070483</v>
+        <v>0.04994502908892631</v>
       </c>
       <c r="W52">
-        <v>0.2237874213836478</v>
+        <v>0.2240229621408312</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1698130989023494</v>
+        <v>0.166483430296421</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5589,22 +5589,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2785537676431814</v>
+        <v>0.2804537676431814</v>
       </c>
       <c r="C53">
-        <v>3.29727125710499</v>
+        <v>2.869264050160428</v>
       </c>
       <c r="D53">
-        <v>17.51347125710499</v>
+        <v>17.37166405016043</v>
       </c>
       <c r="E53">
-        <v>12.2762</v>
+        <v>12.5624</v>
       </c>
       <c r="F53">
-        <v>14.5962</v>
+        <v>14.8824</v>
       </c>
       <c r="G53">
         <v>0.38</v>
@@ -5625,37 +5625,37 @@
         <v>0.573</v>
       </c>
       <c r="M53">
-        <v>3.44178396</v>
+        <v>3.50926992</v>
       </c>
       <c r="N53">
-        <v>-2.86878396</v>
+        <v>-2.93626992</v>
       </c>
       <c r="O53">
-        <v>-0.8606351880000002</v>
+        <v>-0.8808809760000001</v>
       </c>
       <c r="P53">
-        <v>-2.008148772</v>
+        <v>-2.055388944</v>
       </c>
       <c r="Q53">
-        <v>-2.581148772</v>
+        <v>-2.628388944</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3353103203088929</v>
+        <v>0.3413417853153281</v>
       </c>
       <c r="T53">
-        <v>2.47988279045259</v>
+        <v>2.531547015253686</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.04994502908892631</v>
+        <v>0.04898454776029311</v>
       </c>
       <c r="W53">
-        <v>0.2240229621408312</v>
+        <v>0.2242494436381229</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.166483430296421</v>
+        <v>0.1632818258676437</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5671,22 +5671,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2804537676431814</v>
+        <v>0.2823537676431814</v>
       </c>
       <c r="C54">
-        <v>2.869264050160428</v>
+        <v>2.443534834354011</v>
       </c>
       <c r="D54">
-        <v>17.37166405016043</v>
+        <v>17.23213483435401</v>
       </c>
       <c r="E54">
-        <v>12.5624</v>
+        <v>12.8486</v>
       </c>
       <c r="F54">
-        <v>14.8824</v>
+        <v>15.1686</v>
       </c>
       <c r="G54">
         <v>0.38</v>
@@ -5707,37 +5707,37 @@
         <v>0.573</v>
       </c>
       <c r="M54">
-        <v>3.50926992</v>
+        <v>3.57675588</v>
       </c>
       <c r="N54">
-        <v>-2.93626992</v>
+        <v>-3.00375588</v>
       </c>
       <c r="O54">
-        <v>-0.8808809760000001</v>
+        <v>-0.901126764</v>
       </c>
       <c r="P54">
-        <v>-2.055388944</v>
+        <v>-2.102629116</v>
       </c>
       <c r="Q54">
-        <v>-2.628388944</v>
+        <v>-2.675629116</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3413417853153281</v>
+        <v>0.3476299084071436</v>
       </c>
       <c r="T54">
-        <v>2.531547015253686</v>
+        <v>2.585409717705892</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.04898454776029311</v>
+        <v>0.0480603110100989</v>
       </c>
       <c r="W54">
-        <v>0.2242494436381229</v>
+        <v>0.2244673786638187</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1632818258676437</v>
+        <v>0.1602010367003297</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5753,22 +5753,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2823537676431814</v>
+        <v>0.2842537676431814</v>
       </c>
       <c r="C55">
-        <v>2.443534834354011</v>
+        <v>2.020029156574719</v>
       </c>
       <c r="D55">
-        <v>17.23213483435401</v>
+        <v>17.09482915657472</v>
       </c>
       <c r="E55">
-        <v>12.8486</v>
+        <v>13.1348</v>
       </c>
       <c r="F55">
-        <v>15.1686</v>
+        <v>15.4548</v>
       </c>
       <c r="G55">
         <v>0.38</v>
@@ -5789,37 +5789,37 @@
         <v>0.573</v>
       </c>
       <c r="M55">
-        <v>3.57675588</v>
+        <v>3.644241840000001</v>
       </c>
       <c r="N55">
-        <v>-3.00375588</v>
+        <v>-3.071241840000001</v>
       </c>
       <c r="O55">
-        <v>-0.901126764</v>
+        <v>-0.9213725520000002</v>
       </c>
       <c r="P55">
-        <v>-2.102629116</v>
+        <v>-2.149869288000001</v>
       </c>
       <c r="Q55">
-        <v>-2.675629116</v>
+        <v>-2.722869288</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3476299084071436</v>
+        <v>0.3541914281551251</v>
       </c>
       <c r="T55">
-        <v>2.585409717705892</v>
+        <v>2.641614276786455</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.0480603110100989</v>
+        <v>0.04717030525065261</v>
       </c>
       <c r="W55">
-        <v>0.2244673786638187</v>
+        <v>0.2246772420218961</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1602010367003297</v>
+        <v>0.1572343508355087</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5835,22 +5835,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2842537676431814</v>
+        <v>0.2861537676431815</v>
       </c>
       <c r="C56">
-        <v>2.020029156574719</v>
+        <v>1.598694285522017</v>
       </c>
       <c r="D56">
-        <v>17.09482915657472</v>
+        <v>16.95969428552202</v>
       </c>
       <c r="E56">
-        <v>13.1348</v>
+        <v>13.421</v>
       </c>
       <c r="F56">
-        <v>15.4548</v>
+        <v>15.741</v>
       </c>
       <c r="G56">
         <v>0.38</v>
@@ -5871,37 +5871,37 @@
         <v>0.573</v>
       </c>
       <c r="M56">
-        <v>3.644241840000001</v>
+        <v>3.711727800000001</v>
       </c>
       <c r="N56">
-        <v>-3.071241840000001</v>
+        <v>-3.138727800000001</v>
       </c>
       <c r="O56">
-        <v>-0.9213725520000002</v>
+        <v>-0.9416183400000002</v>
       </c>
       <c r="P56">
-        <v>-2.149869288000001</v>
+        <v>-2.197109460000001</v>
       </c>
       <c r="Q56">
-        <v>-2.722869288</v>
+        <v>-2.77010946</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3541914281551251</v>
+        <v>0.3610445710030167</v>
       </c>
       <c r="T56">
-        <v>2.641614276786455</v>
+        <v>2.700316816270599</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04717030525065261</v>
+        <v>0.04631266333700438</v>
       </c>
       <c r="W56">
-        <v>0.2246772420218961</v>
+        <v>0.2248794739851344</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1572343508355087</v>
+        <v>0.1543755444566813</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5917,22 +5917,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2861537676431815</v>
+        <v>0.2880537676431814</v>
       </c>
       <c r="C57">
-        <v>1.598694285522017</v>
+        <v>1.179479144184967</v>
       </c>
       <c r="D57">
-        <v>16.95969428552202</v>
+        <v>16.82667914418497</v>
       </c>
       <c r="E57">
-        <v>13.421</v>
+        <v>13.7072</v>
       </c>
       <c r="F57">
-        <v>15.741</v>
+        <v>16.0272</v>
       </c>
       <c r="G57">
         <v>0.38</v>
@@ -5953,37 +5953,37 @@
         <v>0.573</v>
       </c>
       <c r="M57">
-        <v>3.711727800000001</v>
+        <v>3.77921376</v>
       </c>
       <c r="N57">
-        <v>-3.138727800000001</v>
+        <v>-3.20621376</v>
       </c>
       <c r="O57">
-        <v>-0.9416183400000002</v>
+        <v>-0.961864128</v>
       </c>
       <c r="P57">
-        <v>-2.197109460000001</v>
+        <v>-2.244349632</v>
       </c>
       <c r="Q57">
-        <v>-2.77010946</v>
+        <v>-2.817349632</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3610445710030167</v>
+        <v>0.3682092203439944</v>
       </c>
       <c r="T57">
-        <v>2.700316816270599</v>
+        <v>2.761687653004021</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04631266333700438</v>
+        <v>0.04548565149170074</v>
       </c>
       <c r="W57">
-        <v>0.2248794739851344</v>
+        <v>0.225074483378257</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1543755444566813</v>
+        <v>0.1516188383056691</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5999,22 +5999,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2880537676431814</v>
+        <v>0.2899537676431814</v>
       </c>
       <c r="C58">
-        <v>1.179479144184967</v>
+        <v>0.7623342454739408</v>
       </c>
       <c r="D58">
-        <v>16.82667914418497</v>
+        <v>16.69573424547394</v>
       </c>
       <c r="E58">
-        <v>13.7072</v>
+        <v>13.9934</v>
       </c>
       <c r="F58">
-        <v>16.0272</v>
+        <v>16.3134</v>
       </c>
       <c r="G58">
         <v>0.38</v>
@@ -6035,37 +6035,37 @@
         <v>0.573</v>
       </c>
       <c r="M58">
-        <v>3.77921376</v>
+        <v>3.846699720000001</v>
       </c>
       <c r="N58">
-        <v>-3.20621376</v>
+        <v>-3.273699720000001</v>
       </c>
       <c r="O58">
-        <v>-0.961864128</v>
+        <v>-0.9821099160000002</v>
       </c>
       <c r="P58">
-        <v>-2.244349632</v>
+        <v>-2.291589804</v>
       </c>
       <c r="Q58">
-        <v>-2.817349632</v>
+        <v>-2.864589804</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3682092203439944</v>
+        <v>0.3757071091892035</v>
       </c>
       <c r="T58">
-        <v>2.761687653004021</v>
+        <v>2.825912947259928</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04548565149170074</v>
+        <v>0.04468765760588143</v>
       </c>
       <c r="W58">
-        <v>0.225074483378257</v>
+        <v>0.2252626503365332</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1516188383056691</v>
+        <v>0.1489588586862715</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6081,22 +6081,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2899537676431814</v>
+        <v>0.2918537676431814</v>
       </c>
       <c r="C59">
-        <v>0.7623342454739408</v>
+        <v>0.3472116308346784</v>
       </c>
       <c r="D59">
-        <v>16.69573424547394</v>
+        <v>16.56681163083468</v>
       </c>
       <c r="E59">
-        <v>13.9934</v>
+        <v>14.2796</v>
       </c>
       <c r="F59">
-        <v>16.3134</v>
+        <v>16.5996</v>
       </c>
       <c r="G59">
         <v>0.38</v>
@@ -6117,37 +6117,37 @@
         <v>0.573</v>
       </c>
       <c r="M59">
-        <v>3.846699720000001</v>
+        <v>3.914185680000001</v>
       </c>
       <c r="N59">
-        <v>-3.273699720000001</v>
+        <v>-3.341185680000001</v>
       </c>
       <c r="O59">
-        <v>-0.9821099160000002</v>
+        <v>-1.002355704</v>
       </c>
       <c r="P59">
-        <v>-2.291589804</v>
+        <v>-2.338829976</v>
       </c>
       <c r="Q59">
-        <v>-2.864589804</v>
+        <v>-2.911829976</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3757071091892035</v>
+        <v>0.383562040360375</v>
       </c>
       <c r="T59">
-        <v>2.825912947259928</v>
+        <v>2.893196588861355</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04468765760588143</v>
+        <v>0.04391718075060761</v>
       </c>
       <c r="W59">
-        <v>0.2252626503365332</v>
+        <v>0.2254443287790067</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1489588586862715</v>
+        <v>0.1463906025020254</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2918537676431814</v>
+        <v>0.2937537676431814</v>
       </c>
       <c r="C60">
-        <v>0.347211630834682</v>
+        <v>-0.06593518831542156</v>
       </c>
       <c r="D60">
-        <v>16.56681163083468</v>
+        <v>16.43986481168458</v>
       </c>
       <c r="E60">
-        <v>14.2796</v>
+        <v>14.5658</v>
       </c>
       <c r="F60">
-        <v>16.5996</v>
+        <v>16.8858</v>
       </c>
       <c r="G60">
         <v>0.38</v>
@@ -6199,37 +6199,37 @@
         <v>0.573</v>
       </c>
       <c r="M60">
-        <v>3.91418568</v>
+        <v>3.98167164</v>
       </c>
       <c r="N60">
-        <v>-3.34118568</v>
+        <v>-3.40867164</v>
       </c>
       <c r="O60">
-        <v>-1.002355704</v>
+        <v>-1.022601492</v>
       </c>
       <c r="P60">
-        <v>-2.338829976</v>
+        <v>-2.386070148</v>
       </c>
       <c r="Q60">
-        <v>-2.911829975999999</v>
+        <v>-2.959070148</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.383562040360375</v>
+        <v>0.3918001389057499</v>
       </c>
       <c r="T60">
-        <v>2.893196588861355</v>
+        <v>2.963762359321388</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04391718075060762</v>
+        <v>0.0431728217548346</v>
       </c>
       <c r="W60">
-        <v>0.2254443287790067</v>
+        <v>0.22561984863021</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1463906025020254</v>
+        <v>0.1439094058494487</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6245,22 +6245,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2937537676431814</v>
+        <v>0.2956537676431814</v>
       </c>
       <c r="C61">
-        <v>-0.06593518831542156</v>
+        <v>-0.4771512864789287</v>
       </c>
       <c r="D61">
-        <v>16.43986481168458</v>
+        <v>16.31484871352107</v>
       </c>
       <c r="E61">
-        <v>14.5658</v>
+        <v>14.852</v>
       </c>
       <c r="F61">
-        <v>16.8858</v>
+        <v>17.172</v>
       </c>
       <c r="G61">
         <v>0.38</v>
@@ -6281,37 +6281,37 @@
         <v>0.573</v>
       </c>
       <c r="M61">
-        <v>3.98167164</v>
+        <v>4.0491576</v>
       </c>
       <c r="N61">
-        <v>-3.40867164</v>
+        <v>-3.4761576</v>
       </c>
       <c r="O61">
-        <v>-1.022601492</v>
+        <v>-1.04284728</v>
       </c>
       <c r="P61">
-        <v>-2.386070148</v>
+        <v>-2.43331032</v>
       </c>
       <c r="Q61">
-        <v>-2.959070148</v>
+        <v>-3.00631032</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3918001389057499</v>
+        <v>0.4004501423783937</v>
       </c>
       <c r="T61">
-        <v>2.963762359321388</v>
+        <v>3.037856418304422</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.0431728217548346</v>
+        <v>0.04245327472558736</v>
       </c>
       <c r="W61">
-        <v>0.22561984863021</v>
+        <v>0.2257895178197065</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1439094058494487</v>
+        <v>0.1415109157519578</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6327,22 +6327,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2956537676431814</v>
+        <v>0.2975537676431814</v>
       </c>
       <c r="C62">
-        <v>-0.4771512864789287</v>
+        <v>-0.886480377439046</v>
       </c>
       <c r="D62">
-        <v>16.31484871352107</v>
+        <v>16.19171962256096</v>
       </c>
       <c r="E62">
-        <v>14.852</v>
+        <v>15.1382</v>
       </c>
       <c r="F62">
-        <v>17.172</v>
+        <v>17.4582</v>
       </c>
       <c r="G62">
         <v>0.38</v>
@@ -6363,37 +6363,37 @@
         <v>0.573</v>
       </c>
       <c r="M62">
-        <v>4.0491576</v>
+        <v>4.116643560000001</v>
       </c>
       <c r="N62">
-        <v>-3.4761576</v>
+        <v>-3.543643560000001</v>
       </c>
       <c r="O62">
-        <v>-1.04284728</v>
+        <v>-1.063093068</v>
       </c>
       <c r="P62">
-        <v>-2.43331032</v>
+        <v>-2.480550492000001</v>
       </c>
       <c r="Q62">
-        <v>-3.00631032</v>
+        <v>-3.053550492000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4004501423783937</v>
+        <v>0.4095437357727115</v>
       </c>
       <c r="T62">
-        <v>3.037856418304422</v>
+        <v>3.115750172619921</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04245327472558736</v>
+        <v>0.04175731940221707</v>
       </c>
       <c r="W62">
-        <v>0.2257895178197065</v>
+        <v>0.2259536240849572</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1415109157519578</v>
+        <v>0.139191064674057</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6409,22 +6409,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2975537676431814</v>
+        <v>0.2994537676431814</v>
       </c>
       <c r="C63">
-        <v>-0.886480377439046</v>
+        <v>-1.293964865222179</v>
       </c>
       <c r="D63">
-        <v>16.19171962256096</v>
+        <v>16.07043513477782</v>
       </c>
       <c r="E63">
-        <v>15.1382</v>
+        <v>15.4244</v>
       </c>
       <c r="F63">
-        <v>17.4582</v>
+        <v>17.7444</v>
       </c>
       <c r="G63">
         <v>0.38</v>
@@ -6445,37 +6445,37 @@
         <v>0.573</v>
       </c>
       <c r="M63">
-        <v>4.116643560000001</v>
+        <v>4.18412952</v>
       </c>
       <c r="N63">
-        <v>-3.543643560000001</v>
+        <v>-3.61112952</v>
       </c>
       <c r="O63">
-        <v>-1.063093068</v>
+        <v>-1.083338856</v>
       </c>
       <c r="P63">
-        <v>-2.480550492000001</v>
+        <v>-2.527790664</v>
       </c>
       <c r="Q63">
-        <v>-3.053550492000001</v>
+        <v>-3.100790664</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4095437357727115</v>
+        <v>0.4191159393456776</v>
       </c>
       <c r="T63">
-        <v>3.115750172619921</v>
+        <v>3.197743598215181</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04175731940221707</v>
+        <v>0.04108381425056842</v>
       </c>
       <c r="W63">
-        <v>0.2259536240849572</v>
+        <v>0.226112436599716</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.139191064674057</v>
+        <v>0.1369460475018948</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6491,22 +6491,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2994537676431814</v>
+        <v>0.3013537676431814</v>
       </c>
       <c r="C64">
-        <v>-1.293964865222179</v>
+        <v>-1.699645892787036</v>
       </c>
       <c r="D64">
-        <v>16.07043513477782</v>
+        <v>15.95095410721297</v>
       </c>
       <c r="E64">
-        <v>15.4244</v>
+        <v>15.7106</v>
       </c>
       <c r="F64">
-        <v>17.7444</v>
+        <v>18.0306</v>
       </c>
       <c r="G64">
         <v>0.38</v>
@@ -6527,37 +6527,37 @@
         <v>0.573</v>
       </c>
       <c r="M64">
-        <v>4.18412952</v>
+        <v>4.25161548</v>
       </c>
       <c r="N64">
-        <v>-3.61112952</v>
+        <v>-3.67861548</v>
       </c>
       <c r="O64">
-        <v>-1.083338856</v>
+        <v>-1.103584644</v>
       </c>
       <c r="P64">
-        <v>-2.527790664</v>
+        <v>-2.575030836</v>
       </c>
       <c r="Q64">
-        <v>-3.100790664</v>
+        <v>-3.148030836</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4191159393456776</v>
+        <v>0.4292055593279932</v>
       </c>
       <c r="T64">
-        <v>3.197743598215181</v>
+        <v>3.284169100869646</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04108381425056842</v>
+        <v>0.04043169021484511</v>
       </c>
       <c r="W64">
-        <v>0.226112436599716</v>
+        <v>0.2262662074473395</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1369460475018948</v>
+        <v>0.1347723007161503</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6573,22 +6573,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.3013537676431814</v>
+        <v>0.3032537676431814</v>
       </c>
       <c r="C65">
-        <v>-1.699645892787036</v>
+        <v>-2.103563388557806</v>
       </c>
       <c r="D65">
-        <v>15.95095410721297</v>
+        <v>15.83323661144219</v>
       </c>
       <c r="E65">
-        <v>15.7106</v>
+        <v>15.9968</v>
       </c>
       <c r="F65">
-        <v>18.0306</v>
+        <v>18.3168</v>
       </c>
       <c r="G65">
         <v>0.38</v>
@@ -6609,37 +6609,37 @@
         <v>0.573</v>
       </c>
       <c r="M65">
-        <v>4.25161548</v>
+        <v>4.319101440000001</v>
       </c>
       <c r="N65">
-        <v>-3.67861548</v>
+        <v>-3.746101440000001</v>
       </c>
       <c r="O65">
-        <v>-1.103584644</v>
+        <v>-1.123830432</v>
       </c>
       <c r="P65">
-        <v>-2.575030836</v>
+        <v>-2.622271008000001</v>
       </c>
       <c r="Q65">
-        <v>-3.148030836</v>
+        <v>-3.195271008000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4292055593279932</v>
+        <v>0.4398557137537709</v>
       </c>
       <c r="T65">
-        <v>3.284169100869646</v>
+        <v>3.375396020338248</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04043169021484511</v>
+        <v>0.03979994505523814</v>
       </c>
       <c r="W65">
-        <v>0.2262662074473395</v>
+        <v>0.2264151729559749</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1347723007161503</v>
+        <v>0.1326664835174605</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6655,22 +6655,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.3032537676431814</v>
+        <v>0.3051537676431814</v>
       </c>
       <c r="C66">
-        <v>-2.103563388557806</v>
+        <v>-2.505756110911967</v>
       </c>
       <c r="D66">
-        <v>15.83323661144219</v>
+        <v>15.71724388908804</v>
       </c>
       <c r="E66">
-        <v>15.9968</v>
+        <v>16.283</v>
       </c>
       <c r="F66">
-        <v>18.3168</v>
+        <v>18.603</v>
       </c>
       <c r="G66">
         <v>0.38</v>
@@ -6691,37 +6691,37 @@
         <v>0.573</v>
       </c>
       <c r="M66">
-        <v>4.319101440000001</v>
+        <v>4.386587400000001</v>
       </c>
       <c r="N66">
-        <v>-3.746101440000001</v>
+        <v>-3.813587400000001</v>
       </c>
       <c r="O66">
-        <v>-1.123830432</v>
+        <v>-1.14407622</v>
       </c>
       <c r="P66">
-        <v>-2.622271008000001</v>
+        <v>-2.669511180000001</v>
       </c>
       <c r="Q66">
-        <v>-3.195271008000001</v>
+        <v>-3.242511180000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4398557137537709</v>
+        <v>0.4511144484324501</v>
       </c>
       <c r="T66">
-        <v>3.375396020338248</v>
+        <v>3.471835906633627</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03979994505523814</v>
+        <v>0.03918763820823448</v>
       </c>
       <c r="W66">
-        <v>0.2264151729559749</v>
+        <v>0.2265595549104983</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1326664835174605</v>
+        <v>0.130625460694115</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6737,22 +6737,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.3051537676431814</v>
+        <v>0.3070537676431814</v>
       </c>
       <c r="C67">
-        <v>-2.505756110911967</v>
+        <v>-2.906261690726808</v>
       </c>
       <c r="D67">
-        <v>15.71724388908804</v>
+        <v>15.60293830927319</v>
       </c>
       <c r="E67">
-        <v>16.283</v>
+        <v>16.5692</v>
       </c>
       <c r="F67">
-        <v>18.603</v>
+        <v>18.8892</v>
       </c>
       <c r="G67">
         <v>0.38</v>
@@ -6773,37 +6773,37 @@
         <v>0.573</v>
       </c>
       <c r="M67">
-        <v>4.386587400000001</v>
+        <v>4.454073360000001</v>
       </c>
       <c r="N67">
-        <v>-3.813587400000001</v>
+        <v>-3.881073360000001</v>
       </c>
       <c r="O67">
-        <v>-1.14407622</v>
+        <v>-1.164322008</v>
       </c>
       <c r="P67">
-        <v>-2.669511180000001</v>
+        <v>-2.716751352000001</v>
       </c>
       <c r="Q67">
-        <v>-3.242511180000001</v>
+        <v>-3.289751352000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4511144484324501</v>
+        <v>0.4630354616216397</v>
       </c>
       <c r="T67">
-        <v>3.471835906633627</v>
+        <v>3.573948727416968</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03918763820823448</v>
+        <v>0.03859388611417032</v>
       </c>
       <c r="W67">
-        <v>0.2265595549104983</v>
+        <v>0.2266995616542786</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.130625460694115</v>
+        <v>0.1286462870472345</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6819,22 +6819,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.3070537676431814</v>
+        <v>0.3089537676431814</v>
       </c>
       <c r="C68">
-        <v>-2.906261690726808</v>
+        <v>-3.305116672082869</v>
       </c>
       <c r="D68">
-        <v>15.60293830927319</v>
+        <v>15.49028332791713</v>
       </c>
       <c r="E68">
-        <v>16.5692</v>
+        <v>16.8554</v>
       </c>
       <c r="F68">
-        <v>18.8892</v>
+        <v>19.1754</v>
       </c>
       <c r="G68">
         <v>0.38</v>
@@ -6855,37 +6855,37 @@
         <v>0.573</v>
       </c>
       <c r="M68">
-        <v>4.454073360000001</v>
+        <v>4.521559320000001</v>
       </c>
       <c r="N68">
-        <v>-3.881073360000001</v>
+        <v>-3.948559320000001</v>
       </c>
       <c r="O68">
-        <v>-1.164322008</v>
+        <v>-1.184567796</v>
       </c>
       <c r="P68">
-        <v>-2.716751352000001</v>
+        <v>-2.763991524000001</v>
       </c>
       <c r="Q68">
-        <v>-3.289751352000001</v>
+        <v>-3.336991524000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4630354616216397</v>
+        <v>0.4756789604586591</v>
       </c>
       <c r="T68">
-        <v>3.573948727416968</v>
+        <v>3.682250204005361</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03859388611417032</v>
+        <v>0.03801785796321255</v>
       </c>
       <c r="W68">
-        <v>0.2266995616542786</v>
+        <v>0.2268353890922745</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1286462870472345</v>
+        <v>0.1267261932107085</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6901,22 +6901,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.3089537676431814</v>
+        <v>0.3108537676431814</v>
       </c>
       <c r="C69">
-        <v>-3.305116672082869</v>
+        <v>-3.702356551216612</v>
       </c>
       <c r="D69">
-        <v>15.49028332791713</v>
+        <v>15.37924344878339</v>
       </c>
       <c r="E69">
-        <v>16.8554</v>
+        <v>17.1416</v>
       </c>
       <c r="F69">
-        <v>19.1754</v>
+        <v>19.4616</v>
       </c>
       <c r="G69">
         <v>0.38</v>
@@ -6937,37 +6937,37 @@
         <v>0.573</v>
       </c>
       <c r="M69">
-        <v>4.521559320000001</v>
+        <v>4.589045280000001</v>
       </c>
       <c r="N69">
-        <v>-3.948559320000001</v>
+        <v>-4.01604528</v>
       </c>
       <c r="O69">
-        <v>-1.184567796</v>
+        <v>-1.204813584</v>
       </c>
       <c r="P69">
-        <v>-2.763991524000001</v>
+        <v>-2.811231696</v>
       </c>
       <c r="Q69">
-        <v>-3.336991524000001</v>
+        <v>-3.384231696</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4756789604586591</v>
+        <v>0.4891126779729922</v>
       </c>
       <c r="T69">
-        <v>3.682250204005361</v>
+        <v>3.797320522880529</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03801785796321255</v>
+        <v>0.03745877181669473</v>
       </c>
       <c r="W69">
-        <v>0.2268353890922745</v>
+        <v>0.2269672216056234</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1267261932107085</v>
+        <v>0.1248625727223158</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6983,22 +6983,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.3108537676431814</v>
+        <v>0.3127537676431814</v>
       </c>
       <c r="C70">
-        <v>-3.702356551216612</v>
+        <v>-4.098015813809775</v>
       </c>
       <c r="D70">
-        <v>15.37924344878339</v>
+        <v>15.26978418619023</v>
       </c>
       <c r="E70">
-        <v>17.1416</v>
+        <v>17.4278</v>
       </c>
       <c r="F70">
-        <v>19.4616</v>
+        <v>19.7478</v>
       </c>
       <c r="G70">
         <v>0.38</v>
@@ -7019,37 +7019,37 @@
         <v>0.573</v>
       </c>
       <c r="M70">
-        <v>4.589045280000001</v>
+        <v>4.656531240000001</v>
       </c>
       <c r="N70">
-        <v>-4.01604528</v>
+        <v>-4.083531240000001</v>
       </c>
       <c r="O70">
-        <v>-1.204813584</v>
+        <v>-1.225059372</v>
       </c>
       <c r="P70">
-        <v>-2.811231696</v>
+        <v>-2.858471868000001</v>
       </c>
       <c r="Q70">
-        <v>-3.384231696</v>
+        <v>-3.431471868</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4891126779729922</v>
+        <v>0.503413086939863</v>
       </c>
       <c r="T70">
-        <v>3.797320522880529</v>
+        <v>3.91981473329603</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03745877181669473</v>
+        <v>0.03691589106572814</v>
       </c>
       <c r="W70">
-        <v>0.2269672216056234</v>
+        <v>0.2270952328867013</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1248625727223158</v>
+        <v>0.1230529702190937</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7065,22 +7065,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.3127537676431814</v>
+        <v>0.3146537676431814</v>
       </c>
       <c r="C71">
-        <v>-4.098015813809775</v>
+        <v>-4.492127970697481</v>
       </c>
       <c r="D71">
-        <v>15.26978418619023</v>
+        <v>15.16187202930252</v>
       </c>
       <c r="E71">
-        <v>17.4278</v>
+        <v>17.714</v>
       </c>
       <c r="F71">
-        <v>19.7478</v>
+        <v>20.034</v>
       </c>
       <c r="G71">
         <v>0.38</v>
@@ -7101,37 +7101,37 @@
         <v>0.573</v>
       </c>
       <c r="M71">
-        <v>4.656531240000001</v>
+        <v>4.7240172</v>
       </c>
       <c r="N71">
-        <v>-4.083531240000001</v>
+        <v>-4.1510172</v>
       </c>
       <c r="O71">
-        <v>-1.225059372</v>
+        <v>-1.24530516</v>
       </c>
       <c r="P71">
-        <v>-2.858471868000001</v>
+        <v>-2.90571204</v>
       </c>
       <c r="Q71">
-        <v>-3.431471868</v>
+        <v>-3.47871204</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.503413086939863</v>
+        <v>0.518666856504525</v>
       </c>
       <c r="T71">
-        <v>3.91981473329603</v>
+        <v>4.050475224405898</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03691589106572814</v>
+        <v>0.03638852119336059</v>
       </c>
       <c r="W71">
-        <v>0.2270952328867013</v>
+        <v>0.2272195867026056</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1230529702190937</v>
+        <v>0.1212950706445354</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7147,22 +7147,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3146537676431814</v>
+        <v>0.3165537676431814</v>
       </c>
       <c r="C72">
-        <v>-4.492127970697481</v>
+        <v>-4.884725592072925</v>
       </c>
       <c r="D72">
-        <v>15.16187202930252</v>
+        <v>15.05547440792708</v>
       </c>
       <c r="E72">
-        <v>17.714</v>
+        <v>18.0002</v>
       </c>
       <c r="F72">
-        <v>20.034</v>
+        <v>20.3202</v>
       </c>
       <c r="G72">
         <v>0.38</v>
@@ -7183,37 +7183,37 @@
         <v>0.573</v>
       </c>
       <c r="M72">
-        <v>4.7240172</v>
+        <v>4.791503160000001</v>
       </c>
       <c r="N72">
-        <v>-4.1510172</v>
+        <v>-4.218503160000001</v>
       </c>
       <c r="O72">
-        <v>-1.24530516</v>
+        <v>-1.265550948</v>
       </c>
       <c r="P72">
-        <v>-2.90571204</v>
+        <v>-2.952952212</v>
       </c>
       <c r="Q72">
-        <v>-3.47871204</v>
+        <v>-3.525952212</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.518666856504525</v>
+        <v>0.534972610177095</v>
       </c>
       <c r="T72">
-        <v>4.050475224405898</v>
+        <v>4.190146783868171</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03638852119336059</v>
+        <v>0.03587600681035551</v>
       </c>
       <c r="W72">
-        <v>0.2272195867026056</v>
+        <v>0.2273404375941182</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1212950706445354</v>
+        <v>0.1195866893678518</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7229,22 +7229,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.3165537676431814</v>
+        <v>0.3184537676431813</v>
       </c>
       <c r="C73">
-        <v>-4.884725592072922</v>
+        <v>-5.275840340261903</v>
       </c>
       <c r="D73">
-        <v>15.05547440792708</v>
+        <v>14.9505596597381</v>
       </c>
       <c r="E73">
-        <v>18.0002</v>
+        <v>18.2864</v>
       </c>
       <c r="F73">
-        <v>20.3202</v>
+        <v>20.6064</v>
       </c>
       <c r="G73">
         <v>0.38</v>
@@ -7265,37 +7265,37 @@
         <v>0.573</v>
       </c>
       <c r="M73">
-        <v>4.79150316</v>
+        <v>4.85898912</v>
       </c>
       <c r="N73">
-        <v>-4.218503160000001</v>
+        <v>-4.28598912</v>
       </c>
       <c r="O73">
-        <v>-1.265550948</v>
+        <v>-1.285796736</v>
       </c>
       <c r="P73">
-        <v>-2.952952212</v>
+        <v>-3.000192384</v>
       </c>
       <c r="Q73">
-        <v>-3.525952212</v>
+        <v>-3.573192384</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.5349726101770947</v>
+        <v>0.5524430605405624</v>
       </c>
       <c r="T73">
-        <v>4.190146783868169</v>
+        <v>4.339794883292032</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03587600681035551</v>
+        <v>0.03537772893798947</v>
       </c>
       <c r="W73">
-        <v>0.2273404375941182</v>
+        <v>0.2274579315164221</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1195866893678517</v>
+        <v>0.1179257631266316</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7311,22 +7311,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.3184537676431813</v>
+        <v>0.3203537676431814</v>
       </c>
       <c r="C74">
-        <v>-5.275840340261903</v>
+        <v>-5.665503001136473</v>
       </c>
       <c r="D74">
-        <v>14.9505596597381</v>
+        <v>14.84709699886353</v>
       </c>
       <c r="E74">
-        <v>18.2864</v>
+        <v>18.5726</v>
       </c>
       <c r="F74">
-        <v>20.6064</v>
+        <v>20.8926</v>
       </c>
       <c r="G74">
         <v>0.38</v>
@@ -7347,37 +7347,37 @@
         <v>0.573</v>
       </c>
       <c r="M74">
-        <v>4.85898912</v>
+        <v>4.92647508</v>
       </c>
       <c r="N74">
-        <v>-4.28598912</v>
+        <v>-4.353475080000001</v>
       </c>
       <c r="O74">
-        <v>-1.285796736</v>
+        <v>-1.306042524</v>
       </c>
       <c r="P74">
-        <v>-3.000192384</v>
+        <v>-3.047432556</v>
       </c>
       <c r="Q74">
-        <v>-3.573192384</v>
+        <v>-3.620432556</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.5524430605405624</v>
+        <v>0.571207618338361</v>
       </c>
       <c r="T74">
-        <v>4.339794883292032</v>
+        <v>4.500528027117663</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03537772893798947</v>
+        <v>0.03489310251418139</v>
       </c>
       <c r="W74">
-        <v>0.2274579315164221</v>
+        <v>0.227572206427156</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1179257631266316</v>
+        <v>0.1163103417139378</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7393,22 +7393,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.3203537676431814</v>
+        <v>0.3222537676431814</v>
       </c>
       <c r="C75">
-        <v>-5.665503001136473</v>
+        <v>-6.053743514233227</v>
       </c>
       <c r="D75">
-        <v>14.84709699886353</v>
+        <v>14.74505648576677</v>
       </c>
       <c r="E75">
-        <v>18.5726</v>
+        <v>18.8588</v>
       </c>
       <c r="F75">
-        <v>20.8926</v>
+        <v>21.1788</v>
       </c>
       <c r="G75">
         <v>0.38</v>
@@ -7429,37 +7429,37 @@
         <v>0.573</v>
       </c>
       <c r="M75">
-        <v>4.92647508</v>
+        <v>4.99396104</v>
       </c>
       <c r="N75">
-        <v>-4.353475080000001</v>
+        <v>-4.42096104</v>
       </c>
       <c r="O75">
-        <v>-1.306042524</v>
+        <v>-1.326288312</v>
       </c>
       <c r="P75">
-        <v>-3.047432556</v>
+        <v>-3.094672728</v>
       </c>
       <c r="Q75">
-        <v>-3.620432556</v>
+        <v>-3.667672728</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.571207618338361</v>
+        <v>0.5914156036590672</v>
       </c>
       <c r="T75">
-        <v>4.500528027117663</v>
+        <v>4.673625258929881</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03489310251418139</v>
+        <v>0.03442157410182759</v>
       </c>
       <c r="W75">
-        <v>0.227572206427156</v>
+        <v>0.2276833928267891</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1163103417139378</v>
+        <v>0.1147385803394254</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7475,22 +7475,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3222537676431814</v>
+        <v>0.3241537676431814</v>
       </c>
       <c r="C76">
-        <v>-6.053743514233227</v>
+        <v>-6.440591001638069</v>
       </c>
       <c r="D76">
-        <v>14.74505648576677</v>
+        <v>14.64440899836193</v>
       </c>
       <c r="E76">
-        <v>18.8588</v>
+        <v>19.145</v>
       </c>
       <c r="F76">
-        <v>21.1788</v>
+        <v>21.465</v>
       </c>
       <c r="G76">
         <v>0.38</v>
@@ -7511,37 +7511,37 @@
         <v>0.573</v>
       </c>
       <c r="M76">
-        <v>4.99396104</v>
+        <v>5.061447</v>
       </c>
       <c r="N76">
-        <v>-4.42096104</v>
+        <v>-4.488447000000001</v>
       </c>
       <c r="O76">
-        <v>-1.326288312</v>
+        <v>-1.3465341</v>
       </c>
       <c r="P76">
-        <v>-3.094672728</v>
+        <v>-3.1419129</v>
       </c>
       <c r="Q76">
-        <v>-3.667672728</v>
+        <v>-3.7149129</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5914156036590672</v>
+        <v>0.6132402278054299</v>
       </c>
       <c r="T76">
-        <v>4.673625258929881</v>
+        <v>4.860570269287076</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03442157410182759</v>
+        <v>0.03396261978046989</v>
       </c>
       <c r="W76">
-        <v>0.2276833928267891</v>
+        <v>0.2277916142557652</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1147385803394254</v>
+        <v>0.1132087326015662</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7557,22 +7557,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.3241537676431814</v>
+        <v>0.3260537676431814</v>
       </c>
       <c r="C77">
-        <v>-6.440591001638069</v>
+        <v>-6.826073795696036</v>
       </c>
       <c r="D77">
-        <v>14.64440899836193</v>
+        <v>14.54512620430396</v>
       </c>
       <c r="E77">
-        <v>19.145</v>
+        <v>19.4312</v>
       </c>
       <c r="F77">
-        <v>21.465</v>
+        <v>21.7512</v>
       </c>
       <c r="G77">
         <v>0.38</v>
@@ -7593,37 +7593,37 @@
         <v>0.573</v>
       </c>
       <c r="M77">
-        <v>5.061447</v>
+        <v>5.12893296</v>
       </c>
       <c r="N77">
-        <v>-4.488447000000001</v>
+        <v>-4.55593296</v>
       </c>
       <c r="O77">
-        <v>-1.3465341</v>
+        <v>-1.366779888</v>
       </c>
       <c r="P77">
-        <v>-3.1419129</v>
+        <v>-3.189153072</v>
       </c>
       <c r="Q77">
-        <v>-3.7149129</v>
+        <v>-3.762153072</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.6132402278054299</v>
+        <v>0.6368835706306561</v>
       </c>
       <c r="T77">
-        <v>4.860570269287076</v>
+        <v>5.063094030507371</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03396261978046989</v>
+        <v>0.03351574320441107</v>
       </c>
       <c r="W77">
-        <v>0.2277916142557652</v>
+        <v>0.2278969877523999</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1132087326015662</v>
+        <v>0.1117191440147036</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7639,22 +7639,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3260537676431814</v>
+        <v>0.3279537676431814</v>
       </c>
       <c r="C78">
-        <v>-6.826073795696036</v>
+        <v>-7.210219465601558</v>
       </c>
       <c r="D78">
-        <v>14.54512620430396</v>
+        <v>14.44718053439844</v>
       </c>
       <c r="E78">
-        <v>19.4312</v>
+        <v>19.7174</v>
       </c>
       <c r="F78">
-        <v>21.7512</v>
+        <v>22.0374</v>
       </c>
       <c r="G78">
         <v>0.38</v>
@@ -7675,37 +7675,37 @@
         <v>0.573</v>
       </c>
       <c r="M78">
-        <v>5.12893296</v>
+        <v>5.19641892</v>
       </c>
       <c r="N78">
-        <v>-4.55593296</v>
+        <v>-4.623418920000001</v>
       </c>
       <c r="O78">
-        <v>-1.366779888</v>
+        <v>-1.387025676</v>
       </c>
       <c r="P78">
-        <v>-3.189153072</v>
+        <v>-3.236393244</v>
       </c>
       <c r="Q78">
-        <v>-3.762153072</v>
+        <v>-3.809393244</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.6368835706306561</v>
+        <v>0.66258285631025</v>
       </c>
       <c r="T78">
-        <v>5.063094030507371</v>
+        <v>5.28322855357291</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03351574320441107</v>
+        <v>0.033080473812146</v>
       </c>
       <c r="W78">
-        <v>0.2278969877523999</v>
+        <v>0.227999624275096</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1117191440147036</v>
+        <v>0.1102682460404866</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7721,22 +7721,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3279537676431814</v>
+        <v>0.3298537676431814</v>
       </c>
       <c r="C79">
-        <v>-7.210219465601558</v>
+        <v>-7.593054842921525</v>
       </c>
       <c r="D79">
-        <v>14.44718053439844</v>
+        <v>14.35054515707848</v>
       </c>
       <c r="E79">
-        <v>19.7174</v>
+        <v>20.0036</v>
       </c>
       <c r="F79">
-        <v>22.0374</v>
+        <v>22.3236</v>
       </c>
       <c r="G79">
         <v>0.38</v>
@@ -7757,37 +7757,37 @@
         <v>0.573</v>
       </c>
       <c r="M79">
-        <v>5.19641892</v>
+        <v>5.263904880000001</v>
       </c>
       <c r="N79">
-        <v>-4.623418920000001</v>
+        <v>-4.690904880000001</v>
       </c>
       <c r="O79">
-        <v>-1.387025676</v>
+        <v>-1.407271464</v>
       </c>
       <c r="P79">
-        <v>-3.236393244</v>
+        <v>-3.283633416000001</v>
       </c>
       <c r="Q79">
-        <v>-3.809393244</v>
+        <v>-3.856633416000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.66258285631025</v>
+        <v>0.6906184406879886</v>
       </c>
       <c r="T79">
-        <v>5.28322855357291</v>
+        <v>5.523375306008042</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.033080473812146</v>
+        <v>0.03265636517352873</v>
       </c>
       <c r="W79">
-        <v>0.227999624275096</v>
+        <v>0.2280996290920819</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1102682460404866</v>
+        <v>0.1088545505784291</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7803,22 +7803,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3298537676431814</v>
+        <v>0.3317537676431814</v>
       </c>
       <c r="C80">
-        <v>-7.593054842921525</v>
+        <v>-7.974606046100886</v>
       </c>
       <c r="D80">
-        <v>14.35054515707848</v>
+        <v>14.25519395389912</v>
       </c>
       <c r="E80">
-        <v>20.0036</v>
+        <v>20.2898</v>
       </c>
       <c r="F80">
-        <v>22.3236</v>
+        <v>22.6098</v>
       </c>
       <c r="G80">
         <v>0.38</v>
@@ -7839,37 +7839,37 @@
         <v>0.573</v>
       </c>
       <c r="M80">
-        <v>5.263904880000001</v>
+        <v>5.331390840000001</v>
       </c>
       <c r="N80">
-        <v>-4.690904880000001</v>
+        <v>-4.758390840000001</v>
       </c>
       <c r="O80">
-        <v>-1.407271464</v>
+        <v>-1.427517252</v>
       </c>
       <c r="P80">
-        <v>-3.283633416000001</v>
+        <v>-3.330873588</v>
       </c>
       <c r="Q80">
-        <v>-3.856633416000001</v>
+        <v>-3.903873588</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.6906184406879886</v>
+        <v>0.7213240807207499</v>
       </c>
       <c r="T80">
-        <v>5.523375306008042</v>
+        <v>5.786393177722711</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03265636517352873</v>
+        <v>0.03224299346247141</v>
       </c>
       <c r="W80">
-        <v>0.2280996290920819</v>
+        <v>0.2281971021415493</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1088545505784291</v>
+        <v>0.1074766448749048</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7885,22 +7885,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3317537676431814</v>
+        <v>0.3336537676431814</v>
       </c>
       <c r="C81">
-        <v>-7.974606046100886</v>
+        <v>-8.354898503997708</v>
       </c>
       <c r="D81">
-        <v>14.25519395389912</v>
+        <v>14.16110149600229</v>
       </c>
       <c r="E81">
-        <v>20.2898</v>
+        <v>20.576</v>
       </c>
       <c r="F81">
-        <v>22.6098</v>
+        <v>22.896</v>
       </c>
       <c r="G81">
         <v>0.38</v>
@@ -7921,37 +7921,37 @@
         <v>0.573</v>
       </c>
       <c r="M81">
-        <v>5.331390840000001</v>
+        <v>5.3988768</v>
       </c>
       <c r="N81">
-        <v>-4.758390840000001</v>
+        <v>-4.8258768</v>
       </c>
       <c r="O81">
-        <v>-1.427517252</v>
+        <v>-1.44776304</v>
       </c>
       <c r="P81">
-        <v>-3.330873588</v>
+        <v>-3.37811376</v>
       </c>
       <c r="Q81">
-        <v>-3.903873588</v>
+        <v>-3.95111376</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.7213240807207499</v>
+        <v>0.7551002847567876</v>
       </c>
       <c r="T81">
-        <v>5.786393177722711</v>
+        <v>6.075712836608847</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03224299346247141</v>
+        <v>0.03183995604419052</v>
       </c>
       <c r="W81">
-        <v>0.2281971021415493</v>
+        <v>0.2282921383647799</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1074766448749048</v>
+        <v>0.1061331868139684</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7967,22 +7967,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3336537676431814</v>
+        <v>0.3355537676431813</v>
       </c>
       <c r="C82">
-        <v>-8.354898503997708</v>
+        <v>-8.733956978492291</v>
       </c>
       <c r="D82">
-        <v>14.16110149600229</v>
+        <v>14.06824302150771</v>
       </c>
       <c r="E82">
-        <v>20.576</v>
+        <v>20.8622</v>
       </c>
       <c r="F82">
-        <v>22.896</v>
+        <v>23.1822</v>
       </c>
       <c r="G82">
         <v>0.38</v>
@@ -8003,37 +8003,37 @@
         <v>0.573</v>
       </c>
       <c r="M82">
-        <v>5.3988768</v>
+        <v>5.466362760000001</v>
       </c>
       <c r="N82">
-        <v>-4.8258768</v>
+        <v>-4.89336276</v>
       </c>
       <c r="O82">
-        <v>-1.44776304</v>
+        <v>-1.468008828</v>
       </c>
       <c r="P82">
-        <v>-3.37811376</v>
+        <v>-3.425353932</v>
       </c>
       <c r="Q82">
-        <v>-3.95111376</v>
+        <v>-3.998353932</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.7551002847567876</v>
+        <v>0.7924318786913553</v>
       </c>
       <c r="T82">
-        <v>6.075712836608847</v>
+        <v>6.395487196430365</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03183995604419052</v>
+        <v>0.03144687016710174</v>
       </c>
       <c r="W82">
-        <v>0.2282921383647799</v>
+        <v>0.2283848280145974</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1061331868139684</v>
+        <v>0.1048229005570059</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8049,22 +8049,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3355537676431813</v>
+        <v>0.3374537676431814</v>
       </c>
       <c r="C83">
-        <v>-8.733956978492291</v>
+        <v>-9.111805586212553</v>
       </c>
       <c r="D83">
-        <v>14.06824302150771</v>
+        <v>13.97659441378745</v>
       </c>
       <c r="E83">
-        <v>20.8622</v>
+        <v>21.1484</v>
       </c>
       <c r="F83">
-        <v>23.1822</v>
+        <v>23.4684</v>
       </c>
       <c r="G83">
         <v>0.38</v>
@@ -8085,37 +8085,37 @@
         <v>0.573</v>
       </c>
       <c r="M83">
-        <v>5.466362760000001</v>
+        <v>5.533848720000001</v>
       </c>
       <c r="N83">
-        <v>-4.89336276</v>
+        <v>-4.960848720000001</v>
       </c>
       <c r="O83">
-        <v>-1.468008828</v>
+        <v>-1.488254616</v>
       </c>
       <c r="P83">
-        <v>-3.425353932</v>
+        <v>-3.472594104000001</v>
       </c>
       <c r="Q83">
-        <v>-3.998353932</v>
+        <v>-4.045594104000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.7924318786913553</v>
+        <v>0.8339114275075418</v>
       </c>
       <c r="T83">
-        <v>6.395487196430365</v>
+        <v>6.750792040676497</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03144687016710174</v>
+        <v>0.03106337175042977</v>
       </c>
       <c r="W83">
-        <v>0.2283848280145974</v>
+        <v>0.2284752569412487</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1048229005570059</v>
+        <v>0.1035445725014325</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8131,22 +8131,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3374537676431814</v>
+        <v>0.3393537676431814</v>
       </c>
       <c r="C84">
-        <v>-9.111805586212553</v>
+        <v>-9.488467819415689</v>
       </c>
       <c r="D84">
-        <v>13.97659441378745</v>
+        <v>13.88613218058431</v>
       </c>
       <c r="E84">
-        <v>21.1484</v>
+        <v>21.4346</v>
       </c>
       <c r="F84">
-        <v>23.4684</v>
+        <v>23.7546</v>
       </c>
       <c r="G84">
         <v>0.38</v>
@@ -8167,37 +8167,37 @@
         <v>0.573</v>
       </c>
       <c r="M84">
-        <v>5.533848720000001</v>
+        <v>5.601334680000001</v>
       </c>
       <c r="N84">
-        <v>-4.960848720000001</v>
+        <v>-5.02833468</v>
       </c>
       <c r="O84">
-        <v>-1.488254616</v>
+        <v>-1.508500404</v>
       </c>
       <c r="P84">
-        <v>-3.472594104000001</v>
+        <v>-3.519834276</v>
       </c>
       <c r="Q84">
-        <v>-4.045594104000001</v>
+        <v>-4.092834276</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.8339114275075418</v>
+        <v>0.8802709232432797</v>
       </c>
       <c r="T84">
-        <v>6.750792040676497</v>
+        <v>7.147897454833939</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03106337175042977</v>
+        <v>0.03068911425946074</v>
       </c>
       <c r="W84">
-        <v>0.2284752569412487</v>
+        <v>0.2285635068576192</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1035445725014325</v>
+        <v>0.1022970475315359</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8213,22 +8213,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3393537676431814</v>
+        <v>0.3412537676431814</v>
       </c>
       <c r="C85">
-        <v>-9.488467819415689</v>
+        <v>-9.863966566064178</v>
       </c>
       <c r="D85">
-        <v>13.88613218058431</v>
+        <v>13.79683343393583</v>
       </c>
       <c r="E85">
-        <v>21.4346</v>
+        <v>21.7208</v>
       </c>
       <c r="F85">
-        <v>23.7546</v>
+        <v>24.0408</v>
       </c>
       <c r="G85">
         <v>0.38</v>
@@ -8249,37 +8249,37 @@
         <v>0.573</v>
       </c>
       <c r="M85">
-        <v>5.601334680000001</v>
+        <v>5.668820640000002</v>
       </c>
       <c r="N85">
-        <v>-5.02833468</v>
+        <v>-5.095820640000001</v>
       </c>
       <c r="O85">
-        <v>-1.508500404</v>
+        <v>-1.528746192</v>
       </c>
       <c r="P85">
-        <v>-3.519834276</v>
+        <v>-3.567074448000001</v>
       </c>
       <c r="Q85">
-        <v>-4.092834276</v>
+        <v>-4.140074448000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.8802709232432797</v>
+        <v>0.9324253559459847</v>
       </c>
       <c r="T85">
-        <v>7.147897454833939</v>
+        <v>7.594641045761061</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03068911425946074</v>
+        <v>0.03032376766113382</v>
       </c>
       <c r="W85">
-        <v>0.2285635068576192</v>
+        <v>0.2286496555855047</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1022970475315359</v>
+        <v>0.1010792255371128</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8295,22 +8295,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3412537676431814</v>
+        <v>0.3431537676431814</v>
       </c>
       <c r="C86">
-        <v>-9.863966566064175</v>
+        <v>-10.23832412913206</v>
       </c>
       <c r="D86">
-        <v>13.79683343393583</v>
+        <v>13.70867587086794</v>
       </c>
       <c r="E86">
-        <v>21.7208</v>
+        <v>22.007</v>
       </c>
       <c r="F86">
-        <v>24.0408</v>
+        <v>24.327</v>
       </c>
       <c r="G86">
         <v>0.38</v>
@@ -8331,37 +8331,37 @@
         <v>0.573</v>
       </c>
       <c r="M86">
-        <v>5.668820640000001</v>
+        <v>5.736306600000001</v>
       </c>
       <c r="N86">
-        <v>-5.095820640000001</v>
+        <v>-5.1633066</v>
       </c>
       <c r="O86">
-        <v>-1.528746192</v>
+        <v>-1.54899198</v>
       </c>
       <c r="P86">
-        <v>-3.567074448000001</v>
+        <v>-3.61431462</v>
       </c>
       <c r="Q86">
-        <v>-4.140074448000001</v>
+        <v>-4.18731462</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.9324253559459841</v>
+        <v>0.9915337130090499</v>
       </c>
       <c r="T86">
-        <v>7.594641045761056</v>
+        <v>8.100950448811794</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03032376766113382</v>
+        <v>0.02996701745335578</v>
       </c>
       <c r="W86">
-        <v>0.2286496555855047</v>
+        <v>0.2287337772844987</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1010792255371127</v>
+        <v>0.09989005817785268</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8377,22 +8377,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3431537676431814</v>
+        <v>0.3450537676431815</v>
       </c>
       <c r="C87">
-        <v>-10.23832412913206</v>
+        <v>-10.61156224517579</v>
       </c>
       <c r="D87">
-        <v>13.70867587086794</v>
+        <v>13.62163775482421</v>
       </c>
       <c r="E87">
-        <v>22.007</v>
+        <v>22.2932</v>
       </c>
       <c r="F87">
-        <v>24.327</v>
+        <v>24.6132</v>
       </c>
       <c r="G87">
         <v>0.38</v>
@@ -8413,37 +8413,37 @@
         <v>0.573</v>
       </c>
       <c r="M87">
-        <v>5.736306600000001</v>
+        <v>5.80379256</v>
       </c>
       <c r="N87">
-        <v>-5.1633066</v>
+        <v>-5.230792559999999</v>
       </c>
       <c r="O87">
-        <v>-1.54899198</v>
+        <v>-1.569237768</v>
       </c>
       <c r="P87">
-        <v>-3.61431462</v>
+        <v>-3.661554792</v>
       </c>
       <c r="Q87">
-        <v>-4.18731462</v>
+        <v>-4.234554791999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.9915337130090499</v>
+        <v>1.059086121081125</v>
       </c>
       <c r="T87">
-        <v>8.100950448811794</v>
+        <v>8.679589766584066</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02996701745335578</v>
+        <v>0.02961856376203769</v>
       </c>
       <c r="W87">
-        <v>0.2287337772844987</v>
+        <v>0.2288159426649115</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.09989005817785268</v>
+        <v>0.09872854587345903</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8459,22 +8459,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3450537676431815</v>
+        <v>0.3469537676431814</v>
       </c>
       <c r="C88">
-        <v>-10.61156224517579</v>
+        <v>-10.98370210220202</v>
       </c>
       <c r="D88">
-        <v>13.62163775482421</v>
+        <v>13.53569789779798</v>
       </c>
       <c r="E88">
-        <v>22.2932</v>
+        <v>22.5794</v>
       </c>
       <c r="F88">
-        <v>24.6132</v>
+        <v>24.8994</v>
       </c>
       <c r="G88">
         <v>0.38</v>
@@ -8495,37 +8495,37 @@
         <v>0.573</v>
       </c>
       <c r="M88">
-        <v>5.80379256</v>
+        <v>5.871278520000001</v>
       </c>
       <c r="N88">
-        <v>-5.230792559999999</v>
+        <v>-5.29827852</v>
       </c>
       <c r="O88">
-        <v>-1.569237768</v>
+        <v>-1.589483556</v>
       </c>
       <c r="P88">
-        <v>-3.661554792</v>
+        <v>-3.708794964</v>
       </c>
       <c r="Q88">
-        <v>-4.234554791999999</v>
+        <v>-4.281794963999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.059086121081125</v>
+        <v>1.137031207318135</v>
       </c>
       <c r="T88">
-        <v>8.679589766584066</v>
+        <v>9.347250517859761</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02961856376203769</v>
+        <v>0.02927812050040508</v>
       </c>
       <c r="W88">
-        <v>0.2288159426649115</v>
+        <v>0.2288962191860045</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.09872854587345903</v>
+        <v>0.09759373500135038</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8541,22 +8541,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3469537676431814</v>
+        <v>0.3488537676431814</v>
       </c>
       <c r="C89">
-        <v>-10.98370210220202</v>
+        <v>-11.35476435686337</v>
       </c>
       <c r="D89">
-        <v>13.53569789779798</v>
+        <v>13.45083564313663</v>
       </c>
       <c r="E89">
-        <v>22.5794</v>
+        <v>22.8656</v>
       </c>
       <c r="F89">
-        <v>24.8994</v>
+        <v>25.1856</v>
       </c>
       <c r="G89">
         <v>0.38</v>
@@ -8577,37 +8577,37 @@
         <v>0.573</v>
       </c>
       <c r="M89">
-        <v>5.871278520000001</v>
+        <v>5.938764480000001</v>
       </c>
       <c r="N89">
-        <v>-5.29827852</v>
+        <v>-5.365764480000001</v>
       </c>
       <c r="O89">
-        <v>-1.589483556</v>
+        <v>-1.609729344</v>
       </c>
       <c r="P89">
-        <v>-3.708794964</v>
+        <v>-3.756035136000001</v>
       </c>
       <c r="Q89">
-        <v>-4.281794963999999</v>
+        <v>-4.329035136000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.137031207318135</v>
+        <v>1.227967141261313</v>
       </c>
       <c r="T89">
-        <v>9.347250517859761</v>
+        <v>10.12618806101475</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02927812050040508</v>
+        <v>0.02894541458562774</v>
       </c>
       <c r="W89">
-        <v>0.2288962191860045</v>
+        <v>0.228974671240709</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.09759373500135038</v>
+        <v>0.09648471528542579</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8623,22 +8623,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3488537676431814</v>
+        <v>0.3507537676431814</v>
       </c>
       <c r="C90">
-        <v>-11.35476435686337</v>
+        <v>-11.72476915101126</v>
       </c>
       <c r="D90">
-        <v>13.45083564313663</v>
+        <v>13.36703084898874</v>
       </c>
       <c r="E90">
-        <v>22.8656</v>
+        <v>23.1518</v>
       </c>
       <c r="F90">
-        <v>25.1856</v>
+        <v>25.4718</v>
       </c>
       <c r="G90">
         <v>0.38</v>
@@ -8659,37 +8659,37 @@
         <v>0.573</v>
       </c>
       <c r="M90">
-        <v>5.938764480000001</v>
+        <v>6.006250440000001</v>
       </c>
       <c r="N90">
-        <v>-5.365764480000001</v>
+        <v>-5.43325044</v>
       </c>
       <c r="O90">
-        <v>-1.609729344</v>
+        <v>-1.629975132</v>
       </c>
       <c r="P90">
-        <v>-3.756035136000001</v>
+        <v>-3.803275308</v>
       </c>
       <c r="Q90">
-        <v>-4.329035136000001</v>
+        <v>-4.376275308</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.227967141261313</v>
+        <v>1.335436881375978</v>
       </c>
       <c r="T90">
-        <v>10.12618806101475</v>
+        <v>11.04675061201609</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02894541458562774</v>
+        <v>0.02862018520826114</v>
       </c>
       <c r="W90">
-        <v>0.228974671240709</v>
+        <v>0.229051360327892</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.09648471528542579</v>
+        <v>0.09540061736087058</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8705,22 +8705,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3507537676431814</v>
+        <v>0.3526537676431815</v>
       </c>
       <c r="C91">
-        <v>-11.72476915101126</v>
+        <v>-12.09373612763386</v>
       </c>
       <c r="D91">
-        <v>13.36703084898874</v>
+        <v>13.28426387236615</v>
       </c>
       <c r="E91">
-        <v>23.1518</v>
+        <v>23.438</v>
       </c>
       <c r="F91">
-        <v>25.4718</v>
+        <v>25.758</v>
       </c>
       <c r="G91">
         <v>0.38</v>
@@ -8741,37 +8741,37 @@
         <v>0.573</v>
       </c>
       <c r="M91">
-        <v>6.006250440000001</v>
+        <v>6.0737364</v>
       </c>
       <c r="N91">
-        <v>-5.43325044</v>
+        <v>-5.500736400000001</v>
       </c>
       <c r="O91">
-        <v>-1.629975132</v>
+        <v>-1.65022092</v>
       </c>
       <c r="P91">
-        <v>-3.803275308</v>
+        <v>-3.850515480000001</v>
       </c>
       <c r="Q91">
-        <v>-4.376275308</v>
+        <v>-4.423515480000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.335436881375978</v>
+        <v>1.464400569513575</v>
       </c>
       <c r="T91">
-        <v>11.04675061201609</v>
+        <v>12.15142567321769</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02862018520826114</v>
+        <v>0.02830218315039157</v>
       </c>
       <c r="W91">
-        <v>0.229051360327892</v>
+        <v>0.2291263452131377</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.09540061736087058</v>
+        <v>0.09434061050130516</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8787,22 +8787,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3526537676431815</v>
+        <v>0.3545537676431814</v>
       </c>
       <c r="C92">
-        <v>-12.09373612763386</v>
+        <v>-12.46168444620552</v>
       </c>
       <c r="D92">
-        <v>13.28426387236615</v>
+        <v>13.20251555379449</v>
       </c>
       <c r="E92">
-        <v>23.438</v>
+        <v>23.7242</v>
       </c>
       <c r="F92">
-        <v>25.758</v>
+        <v>26.0442</v>
       </c>
       <c r="G92">
         <v>0.38</v>
@@ -8823,37 +8823,37 @@
         <v>0.573</v>
       </c>
       <c r="M92">
-        <v>6.0737364</v>
+        <v>6.141222360000001</v>
       </c>
       <c r="N92">
-        <v>-5.500736400000001</v>
+        <v>-5.568222360000002</v>
       </c>
       <c r="O92">
-        <v>-1.65022092</v>
+        <v>-1.670466708</v>
       </c>
       <c r="P92">
-        <v>-3.850515480000001</v>
+        <v>-3.897755652000002</v>
       </c>
       <c r="Q92">
-        <v>-4.423515480000001</v>
+        <v>-4.470755652000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.464400569513575</v>
+        <v>1.622022855015084</v>
       </c>
       <c r="T92">
-        <v>12.15142567321769</v>
+        <v>13.50158408135299</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02830218315039157</v>
+        <v>0.02799117014873892</v>
       </c>
       <c r="W92">
-        <v>0.2291263452131377</v>
+        <v>0.2291996820789274</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.09434061050130516</v>
+        <v>0.09330390049579629</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8869,22 +8869,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3545537676431814</v>
+        <v>0.3564537676431814</v>
       </c>
       <c r="C93">
-        <v>-12.46168444620552</v>
+        <v>-12.82863279747297</v>
       </c>
       <c r="D93">
-        <v>13.20251555379449</v>
+        <v>13.12176720252703</v>
       </c>
       <c r="E93">
-        <v>23.7242</v>
+        <v>24.0104</v>
       </c>
       <c r="F93">
-        <v>26.0442</v>
+        <v>26.3304</v>
       </c>
       <c r="G93">
         <v>0.38</v>
@@ -8905,37 +8905,37 @@
         <v>0.573</v>
       </c>
       <c r="M93">
-        <v>6.141222360000001</v>
+        <v>6.20870832</v>
       </c>
       <c r="N93">
-        <v>-5.568222360000002</v>
+        <v>-5.635708320000001</v>
       </c>
       <c r="O93">
-        <v>-1.670466708</v>
+        <v>-1.690712496</v>
       </c>
       <c r="P93">
-        <v>-3.897755652000002</v>
+        <v>-3.944995824000001</v>
       </c>
       <c r="Q93">
-        <v>-4.470755652000001</v>
+        <v>-4.517995824000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.622022855015084</v>
+        <v>1.81905071189197</v>
       </c>
       <c r="T93">
-        <v>13.50158408135299</v>
+        <v>15.18928209152212</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02799117014873892</v>
+        <v>0.0276869182992961</v>
       </c>
       <c r="W93">
-        <v>0.2291996820789274</v>
+        <v>0.229271424665026</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.09330390049579629</v>
+        <v>0.09228972766432031</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8951,22 +8951,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3564537676431814</v>
+        <v>0.3583537676431814</v>
       </c>
       <c r="C94">
-        <v>-12.82863279747297</v>
+        <v>-13.19459941770217</v>
       </c>
       <c r="D94">
-        <v>13.12176720252703</v>
+        <v>13.04200058229783</v>
       </c>
       <c r="E94">
-        <v>24.0104</v>
+        <v>24.2966</v>
       </c>
       <c r="F94">
-        <v>26.3304</v>
+        <v>26.6166</v>
       </c>
       <c r="G94">
         <v>0.38</v>
@@ -8987,37 +8987,37 @@
         <v>0.573</v>
       </c>
       <c r="M94">
-        <v>6.20870832</v>
+        <v>6.27619428</v>
       </c>
       <c r="N94">
-        <v>-5.635708320000001</v>
+        <v>-5.70319428</v>
       </c>
       <c r="O94">
-        <v>-1.690712496</v>
+        <v>-1.710958284</v>
       </c>
       <c r="P94">
-        <v>-3.944995824000001</v>
+        <v>-3.992235996</v>
       </c>
       <c r="Q94">
-        <v>-4.517995824000001</v>
+        <v>-4.565235996</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.81905071189197</v>
+        <v>2.072372242162251</v>
       </c>
       <c r="T94">
-        <v>15.18928209152212</v>
+        <v>17.35917953316814</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0276869182992961</v>
+        <v>0.02738920950037894</v>
       </c>
       <c r="W94">
-        <v>0.229271424665026</v>
+        <v>0.2293416243998107</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.09228972766432031</v>
+        <v>0.09129736500126318</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9033,22 +9033,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3583537676431814</v>
+        <v>0.3602537676431814</v>
       </c>
       <c r="C95">
-        <v>-13.19459941770217</v>
+        <v>-13.5596021024087</v>
       </c>
       <c r="D95">
-        <v>13.04200058229783</v>
+        <v>12.9631978975913</v>
       </c>
       <c r="E95">
-        <v>24.2966</v>
+        <v>24.5828</v>
       </c>
       <c r="F95">
-        <v>26.6166</v>
+        <v>26.9028</v>
       </c>
       <c r="G95">
         <v>0.38</v>
@@ -9069,37 +9069,37 @@
         <v>0.573</v>
       </c>
       <c r="M95">
-        <v>6.27619428</v>
+        <v>6.343680240000001</v>
       </c>
       <c r="N95">
-        <v>-5.70319428</v>
+        <v>-5.770680240000001</v>
       </c>
       <c r="O95">
-        <v>-1.710958284</v>
+        <v>-1.731204072</v>
       </c>
       <c r="P95">
-        <v>-3.992235996</v>
+        <v>-4.039476168</v>
       </c>
       <c r="Q95">
-        <v>-4.565235996</v>
+        <v>-4.612476168000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.072372242162251</v>
+        <v>2.410134282522627</v>
       </c>
       <c r="T95">
-        <v>17.35917953316814</v>
+        <v>20.2523761220295</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02738920950037894</v>
+        <v>0.02709783493122597</v>
       </c>
       <c r="W95">
-        <v>0.2293416243998107</v>
+        <v>0.2294103305232169</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.09129736500126318</v>
+        <v>0.09032611643741995</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9115,22 +9115,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3602537676431814</v>
+        <v>0.3621537676431814</v>
       </c>
       <c r="C96">
-        <v>-13.5596021024087</v>
+        <v>-13.92365821959332</v>
       </c>
       <c r="D96">
-        <v>12.9631978975913</v>
+        <v>12.88534178040668</v>
       </c>
       <c r="E96">
-        <v>24.5828</v>
+        <v>24.869</v>
       </c>
       <c r="F96">
-        <v>26.9028</v>
+        <v>27.189</v>
       </c>
       <c r="G96">
         <v>0.38</v>
@@ -9151,37 +9151,37 @@
         <v>0.573</v>
       </c>
       <c r="M96">
-        <v>6.343680240000001</v>
+        <v>6.411166200000001</v>
       </c>
       <c r="N96">
-        <v>-5.770680240000001</v>
+        <v>-5.838166200000002</v>
       </c>
       <c r="O96">
-        <v>-1.731204072</v>
+        <v>-1.75144986</v>
       </c>
       <c r="P96">
-        <v>-4.039476168</v>
+        <v>-4.086716340000002</v>
       </c>
       <c r="Q96">
-        <v>-4.612476168000001</v>
+        <v>-4.659716340000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.410134282522627</v>
+        <v>2.883001139027154</v>
       </c>
       <c r="T96">
-        <v>20.2523761220295</v>
+        <v>24.30285134643542</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02709783493122597</v>
+        <v>0.02681259456352885</v>
       </c>
       <c r="W96">
-        <v>0.2294103305232169</v>
+        <v>0.2294775902019199</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.09032611643741995</v>
+        <v>0.08937531521176278</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9197,22 +9197,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3621537676431814</v>
+        <v>0.3640537676431814</v>
       </c>
       <c r="C97">
-        <v>-13.92365821959332</v>
+        <v>-14.28678472250349</v>
       </c>
       <c r="D97">
-        <v>12.88534178040668</v>
+        <v>12.80841527749652</v>
       </c>
       <c r="E97">
-        <v>24.869</v>
+        <v>25.1552</v>
       </c>
       <c r="F97">
-        <v>27.189</v>
+        <v>27.4752</v>
       </c>
       <c r="G97">
         <v>0.38</v>
@@ -9233,37 +9233,37 @@
         <v>0.573</v>
       </c>
       <c r="M97">
-        <v>6.411166200000001</v>
+        <v>6.478652160000001</v>
       </c>
       <c r="N97">
-        <v>-5.838166200000002</v>
+        <v>-5.905652160000001</v>
       </c>
       <c r="O97">
-        <v>-1.75144986</v>
+        <v>-1.771695648</v>
       </c>
       <c r="P97">
-        <v>-4.086716340000002</v>
+        <v>-4.133956512000001</v>
       </c>
       <c r="Q97">
-        <v>-4.659716340000001</v>
+        <v>-4.706956512000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.883001139027154</v>
+        <v>3.592301423783944</v>
       </c>
       <c r="T97">
-        <v>24.30285134643542</v>
+        <v>30.37856418304429</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02681259456352885</v>
+        <v>0.0265332967034921</v>
       </c>
       <c r="W97">
-        <v>0.2294775902019199</v>
+        <v>0.2295434486373166</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.08937531521176278</v>
+        <v>0.08844432234497368</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9279,22 +9279,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3640537676431814</v>
+        <v>0.3659537676431814</v>
       </c>
       <c r="C98">
-        <v>-14.28678472250348</v>
+        <v>-14.64899816194039</v>
       </c>
       <c r="D98">
-        <v>12.80841527749652</v>
+        <v>12.73240183805961</v>
       </c>
       <c r="E98">
-        <v>25.1552</v>
+        <v>25.4414</v>
       </c>
       <c r="F98">
-        <v>27.4752</v>
+        <v>27.7614</v>
       </c>
       <c r="G98">
         <v>0.38</v>
@@ -9315,37 +9315,37 @@
         <v>0.573</v>
       </c>
       <c r="M98">
-        <v>6.47865216</v>
+        <v>6.546138120000001</v>
       </c>
       <c r="N98">
-        <v>-5.905652160000001</v>
+        <v>-5.973138120000002</v>
       </c>
       <c r="O98">
-        <v>-1.771695648</v>
+        <v>-1.791941436</v>
       </c>
       <c r="P98">
-        <v>-4.133956512000001</v>
+        <v>-4.181196684000001</v>
       </c>
       <c r="Q98">
-        <v>-4.706956512000001</v>
+        <v>-4.754196684000002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.592301423783934</v>
+        <v>4.774468565045247</v>
       </c>
       <c r="T98">
-        <v>30.3785641830442</v>
+        <v>40.50475224405895</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0265332967034921</v>
+        <v>0.02625975756221898</v>
       </c>
       <c r="W98">
-        <v>0.2295434486373166</v>
+        <v>0.2296079491668288</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.08844432234497357</v>
+        <v>0.08753252520739652</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9361,22 +9361,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3659537676431814</v>
+        <v>0.3678537676431815</v>
       </c>
       <c r="C99">
-        <v>-14.64899816194039</v>
+        <v>-15.01031469813045</v>
       </c>
       <c r="D99">
-        <v>12.73240183805961</v>
+        <v>12.65728530186955</v>
       </c>
       <c r="E99">
-        <v>25.4414</v>
+        <v>25.7276</v>
       </c>
       <c r="F99">
-        <v>27.7614</v>
+        <v>28.0476</v>
       </c>
       <c r="G99">
         <v>0.38</v>
@@ -9397,37 +9397,37 @@
         <v>0.573</v>
       </c>
       <c r="M99">
-        <v>6.546138120000001</v>
+        <v>6.61362408</v>
       </c>
       <c r="N99">
-        <v>-5.973138120000002</v>
+        <v>-6.040624080000001</v>
       </c>
       <c r="O99">
-        <v>-1.791941436</v>
+        <v>-1.812187224</v>
       </c>
       <c r="P99">
-        <v>-4.181196684000001</v>
+        <v>-4.228436856</v>
       </c>
       <c r="Q99">
-        <v>-4.754196684000002</v>
+        <v>-4.801436856</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.774468565045247</v>
+        <v>7.138802847567869</v>
       </c>
       <c r="T99">
-        <v>40.50475224405895</v>
+        <v>60.75712836608841</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02625975756221898</v>
+        <v>0.02599180085240042</v>
       </c>
       <c r="W99">
-        <v>0.2296079491668288</v>
+        <v>0.229671133359004</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.08753252520739652</v>
+        <v>0.08663933617466801</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9443,22 +9443,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3678537676431815</v>
+        <v>0.3697537676431815</v>
       </c>
       <c r="C100">
-        <v>-15.01031469813045</v>
+        <v>-15.37075011217892</v>
       </c>
       <c r="D100">
-        <v>12.65728530186955</v>
+        <v>12.58304988782108</v>
       </c>
       <c r="E100">
-        <v>25.7276</v>
+        <v>26.0138</v>
       </c>
       <c r="F100">
-        <v>28.0476</v>
+        <v>28.3338</v>
       </c>
       <c r="G100">
         <v>0.38</v>
@@ -9479,37 +9479,37 @@
         <v>0.573</v>
       </c>
       <c r="M100">
-        <v>6.61362408</v>
+        <v>6.68111004</v>
       </c>
       <c r="N100">
-        <v>-6.040624080000001</v>
+        <v>-6.10811004</v>
       </c>
       <c r="O100">
-        <v>-1.812187224</v>
+        <v>-1.832433012</v>
       </c>
       <c r="P100">
-        <v>-4.228436856</v>
+        <v>-4.275677028</v>
       </c>
       <c r="Q100">
-        <v>-4.801436856</v>
+        <v>-4.848677027999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>7.138802847567869</v>
+        <v>14.23180569513574</v>
       </c>
       <c r="T100">
-        <v>60.75712836608841</v>
+        <v>121.5142567321768</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02599180085240042</v>
+        <v>0.02572925740944688</v>
       </c>
       <c r="W100">
-        <v>0.229671133359004</v>
+        <v>0.2297330411028524</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9517,91 +9517,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.08663933617466801</v>
+        <v>0.08576419136482305</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3697537676431815</v>
-      </c>
-      <c r="C101">
-        <v>-15.37075011217892</v>
-      </c>
-      <c r="D101">
-        <v>12.58304988782108</v>
-      </c>
-      <c r="E101">
-        <v>26.0138</v>
-      </c>
-      <c r="F101">
-        <v>28.3338</v>
-      </c>
-      <c r="G101">
-        <v>0.38</v>
-      </c>
-      <c r="H101">
-        <v>26.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <v>-0.573</v>
-      </c>
-      <c r="L101">
-        <v>0.573</v>
-      </c>
-      <c r="M101">
-        <v>6.68111004</v>
-      </c>
-      <c r="N101">
-        <v>-6.10811004</v>
-      </c>
-      <c r="O101">
-        <v>-1.832433012</v>
-      </c>
-      <c r="P101">
-        <v>-4.275677028</v>
-      </c>
-      <c r="Q101">
-        <v>-4.848677027999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>14.23180569513574</v>
-      </c>
-      <c r="T101">
-        <v>121.5142567321768</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02572925740944688</v>
-      </c>
-      <c r="W101">
-        <v>0.2297330411028524</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.08576419136482305</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
